--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 03:55:04</t>
+          <t>2026-09-16 04:57:58</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 02:00:00</t>
+          <t>2026-09-16 02:00:00</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -17,11 +17,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manifest'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'How_To_Read'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +44,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7FBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,12 +93,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -488,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 04:57:58</t>
+          <t>2026-09-17 04:52:47</t>
         </is>
       </c>
     </row>
@@ -500,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 02:00:00</t>
+          <t>2026-09-17 02:00:00</t>
         </is>
       </c>
     </row>
@@ -511,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +529,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -531,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -541,7 +549,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -568,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -635,8 +643,1042 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>FC Pro</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 13 days</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 13 days 2 Objectives 52% 48% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 76% 24% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 77% 23% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 78% 22% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 78% 22% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 98% 3% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 96% 4% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 100% 0% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from each of the Premier League and Women's Super League in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 97% 3% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 86% 14% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 79% 21% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>G019</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 90% 10% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>G021</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>G022</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>G024</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 83% 17% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>G025</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 15 days 30 total 2 Objectives 100% 0% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 15 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -647,7 +1689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -671,74 +1713,74 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Objective_Order</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Objective_Name_Raw</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Objective_Text_Raw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reward_Text_Raw</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mode_Text_Raw</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Difficulty_Text_Raw</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Extraction_Method</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Group_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Mission_Group_Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Objective_Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Objective_Order</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Objective_Name_Raw</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Objective_Text_Raw</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Reward_Text_Raw</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Mode_Text_Raw</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Difficulty_Text_Raw</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Campaign_Expires</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Campaign_Deadline_KST</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Campaign_Deadline_ISO</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Extraction_Method</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Objective_Key</t>
@@ -750,8 +1792,5168 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Hit the Pitch</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>FC Pro</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 13 days</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Kick Off</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>FC Pro</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 13 days</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Assist in 3</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Play 2</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Consumables Pack / 500 Coins / Consumable</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>The Final Challenge</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Finesse</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Evo Unlock / Consumable / 1,500 Coins</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Serial Winner</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PL Scorer</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Top Scorer</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Assister</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1,750 Coins / Consumables Pack / Consumable</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Assist 3</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Play 2</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Consumables Pack / 750 Coins / Consumable</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched World Class Challenge objective</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched World Class Challenge objective.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched Professional Challenge objective.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>4,000 Coins / 2,500 Coins</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>4 Completions</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>3 Completions</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2 Completions</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>1 Completion</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Score in 9</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Believe</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Win 1 match in any Football Ultimate Team game mode.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Barbecue Sauce</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from each of the Premier League and Women's Super League in your starting 11.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Stadium Tifo / Stadium Background Tifo</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from each of the premier league and women's super league in your starting 11.||barbecue sauce</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Be a Goldfish</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Unselfish Play</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Football is Life</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Play 1 match in any Football Ultimate Team game mode.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Badge</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Score in 30</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Score in 20</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Assist 20</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Assist 15</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Play 15</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Play 1</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Consumables Pack / Consumable</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2X 84+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points and pack rewards! all rewards are untradeable.||weekly rush points - ea sports fc 27 objectives</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>35,000 Rush Points</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Earn 35,000 points by completing bonuses in Rush.</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x 2x 84+ Gold Players Pack / 83+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>25,000 Rush Points</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Earn 25,000 points by completing bonuses in Rush.</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>83+ Gold Player Pack / 2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>20,000 Rush Points</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Earn 20,000 points by completing bonuses in Rush.</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 20,000 points by completing bonuses in rush.||20,000 rush points</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10,000 Rush Points</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Earn 10,000 points by completing bonuses in Rush.</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2,500 Rush Points</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Earn 2,500 points by completing bonuses in Rush.</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Build your way up to become a Squad Building Master!</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Build your way up to become a Squad Building Master!</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Large Gold Pack</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Complete 25 Squad Building Challenge groups.</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Complete 25 Squad Building Challenge groups.</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Complete 10 Squad Building Challenge groups.</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Complete 10 Squad Building Challenge groups.</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Complete 5 Squad Building Challenge groups.</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Complete 5 Squad Building Challenge groups.</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Play 15</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Play 15 Draft matches.</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Draft matches.</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Draft matches.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Play 50</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Play 50 Co-Op matches.</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Co-Op matches.</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Co-Op matches.</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Score 20</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Score 20 goals as a team in Rush.</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Complete 20 Bonuses</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Complete 20 Rush bonuses.</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Complete 10 Bonuses</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Complete 10 Rush bonuses.</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Play 15</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Play 15 Rush matches.</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Rush matches.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Rush matches.</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges and earn stars to show your foot</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Coin Boost / 5,000 Coins</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>action_line_fallback</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Get acquainted with Live Events matches.</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>1 Of 2 80+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Live Events</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Play 20</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Play 20 Live Events matches.</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Live Events</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Live Events matches.</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Live Events</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Live Events matches.</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Live Events</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Play 15</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Play 15 Squad Battles Matches on any difficulty.</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>G021</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Squad Battles Matches on any difficulty.</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>G021</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Squad Battles Matches on any difficulty.</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>75+ Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>G021</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Play 15</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Play 15 Rivals matches.</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>G022</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Rivals matches.</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>G022</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="3" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Rivals matches.</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>G022</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Play 15</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Play 15 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="3" t="inlineStr"/>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr"/>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="inlineStr"/>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Scoring Success</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Score 2 goals in any FUT game mode.</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>10 SP</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>G025</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/||score 2 goals in any fut game mode.||scoring success</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Score 10</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Score 10 goals in any FUT game mode using an English player.</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>500 SP / 50 SP</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Win 10</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Rush</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -762,7 +6964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -775,10 +6977,790 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Objective_Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Link_Text</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Parent_Text</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign_Expires</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign_Deadline_KST</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign_Deadline_ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 85% 15%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 3 days</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>9/20 02:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FC Pro</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 13 days 2 Objectives 52% 48%</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 13 days</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 76% 24%</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 77% 23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 78% 22%</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 78% 22%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 98% 3%</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 96% 4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0%</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 100% 0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 97% 3%</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 86% 14%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9%</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 79% 21%</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 92% 8%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17%</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 90% 10%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9%</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10%</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11%</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 83% 17%</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 15 days 30 total 2 Objectives 100% 0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 15 days 500 total 5 Objectives 100% 0%</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 15 days</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:G27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -789,7 +7771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -799,10 +7781,579 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Group_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mission_Group_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Page_Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 13 days 2 Objectives 52% 48% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 76% 24% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 77% 23% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 78% 22% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 78% 22% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 98% 3% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 96% 4% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 100% 0% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from each of the Premier League and Women's Super League in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 97% 3% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 86% 14% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 79% 21% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>G019</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 90% 10% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>G021</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>G022</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>G024</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 83% 17% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>G025</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 15 days 30 total 2 Objectives 100% 0% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 15 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -813,7 +8364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -832,8 +8383,47 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TimeoutError: Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>No objective text extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No objective text extracted</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -17,11 +17,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manifest'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'How_To_Read'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 04:52:47</t>
+          <t>2026-09-18 05:01:17</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 02:00:00</t>
+          <t>2026-09-18 02:00:00</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -646,42 +646,30 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 13 days</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>9/30 02:00</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 13 days 2 Objectives 52% 48% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 98% 2% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -690,18 +678,18 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -711,19 +699,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>9/20 02:00</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 2 days 3 Objectives 90% 10% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -732,40 +728,48 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
+          <t>Expires in 12 days</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 76% 24% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 12 days 2 Objectives 63% 37% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -774,18 +778,18 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -795,7 +799,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -807,7 +811,7 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 77% 23% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 96% 4% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -816,18 +820,18 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -837,7 +841,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -849,7 +853,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 78% 22% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -858,18 +862,18 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -891,7 +895,7 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 78% 22% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -900,18 +904,18 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -921,7 +925,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -933,7 +937,7 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 98% 3% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -942,18 +946,18 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -963,7 +967,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -975,7 +979,7 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 96% 4% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 85% 15% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -984,18 +988,18 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1005,7 +1009,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1017,7 +1021,7 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1026,36 +1030,40 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 100% 0% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from each of the Premier League and Women's Super League in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 97% 3% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1070,12 +1078,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1085,7 +1093,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1097,7 +1105,7 @@
       <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 97% 3% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1106,18 +1114,18 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1127,27 +1135,19 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 86% 14% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 95% 5% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1156,18 +1156,18 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 97% 3% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1194,36 +1194,48 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 5 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1232,18 +1244,18 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1253,7 +1265,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
@@ -1261,7 +1273,7 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 79% 21% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1270,18 +1282,18 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1291,7 +1303,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
@@ -1299,7 +1311,7 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1308,18 +1320,18 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1329,7 +1341,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr"/>
@@ -1337,7 +1349,7 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1346,56 +1358,56 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>G019</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 90% 10% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>0</v>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1405,7 +1417,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
@@ -1413,7 +1425,7 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 88% 13% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1426,52 +1438,52 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>G021</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>3</v>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 94% 6% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1481,7 +1493,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
@@ -1489,7 +1501,7 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1498,18 +1510,18 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1519,7 +1531,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
@@ -1527,7 +1539,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1540,145 +1552,221 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>G024</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 83% 17% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>0</v>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 93% 7% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>G024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 92% 8% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>G025</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 88% 12% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 15 days 30 total 2 Objectives 100% 0% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n">
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 14 days 30 total 2 Objectives 91% 9% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>G026</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 15 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="n">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 14 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1689,7 +1777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1798,68 +1886,52 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Hit the Pitch</t>
+          <t>Claim the Armband</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Claim the Armband</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 13 days</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>9/30 02:00</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband||claim the armband</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -1874,68 +1946,52 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Kick Off</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 13 days</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>9/30 02:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband - ea sports fc 27 objectives||claim the armband - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1946,42 +2002,38 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1991,19 +2043,15 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play 1||play 1</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -2014,42 +2062,38 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 500 Coins / Consumable</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2059,19 +2103,15 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play a match in any fut game mode.||play a match in any fut game mode.</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -2086,25 +2126,25 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>The Final Challenge</t>
+          <t>Win 15</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
-        </is>
-      </c>
+          <t>Win 15 matches in Squad Battles on min. World Class difficulty.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Min. World Class</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -2112,12 +2152,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2127,19 +2167,27 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>9/20 02:00</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/||win 15 matches in squad battles on min. world class difficulty.||win 15</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -2150,29 +2198,29 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Finesse</t>
+          <t>Win 12</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Evo Unlock / Consumable / 1,500 Coins</t>
-        </is>
-      </c>
+          <t>Win 12 matches in Squad Battles on min. World Class difficulty.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Min. World Class</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -2180,12 +2228,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2195,19 +2243,27 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>9/20 02:00</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/||win 12 matches in squad battles on min. world class difficulty.||win 12</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -2218,29 +2274,29 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Serial Winner</t>
+          <t>Win 10</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
+          <t>Win 10 matches in Squad Battles on min. World Class difficulty.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Min. World Class</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -2248,12 +2304,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2263,19 +2319,27 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>9/20 02:00</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/||win 10 matches in squad battles on min. world class difficulty.||win 10</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -2286,21 +2350,21 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PL Scorer</t>
+          <t>Hit the Pitch</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
+          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2316,34 +2380,42 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
+          <t>Expires in 12 days</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -2354,21 +2426,21 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Top Scorer</t>
+          <t>Kick Off</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2384,34 +2456,42 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+          <t>Expires in 12 days</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -2422,21 +2502,21 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Assister</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1,750 Coins / Consumables Pack / Consumable</t>
+          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2447,17 +2527,17 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2467,7 +2547,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -2479,7 +2559,7 @@
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -2490,21 +2570,21 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Assist 3</t>
+          <t>Complete the Ones We Watched World Class Challenge objective</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Complete the Ones We Watched World Class Challenge objective.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
+          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2515,17 +2595,17 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -2535,7 +2615,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -2547,7 +2627,7 @@
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -2558,21 +2638,21 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Complete the Ones We Watched Professional Challenge objective.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 750 Coins / Consumable</t>
+          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2583,17 +2663,17 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2603,7 +2683,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -2615,7 +2695,7 @@
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -2626,21 +2706,21 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
+          <t>4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2656,7 +2736,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2683,7 +2763,7 @@
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2694,21 +2774,21 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective</t>
+          <t>The Final Challenge</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective.</t>
+          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
+          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2719,17 +2799,17 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2739,7 +2819,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2751,7 +2831,7 @@
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2762,21 +2842,21 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
+          <t>Finesse</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objective.</t>
+          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
+          <t>Evo Unlock / Consumable / 1,500 Coins</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2787,17 +2867,17 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2807,7 +2887,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -2819,7 +2899,7 @@
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2830,21 +2910,21 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Serial Winner</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,500 Coins</t>
+          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2855,17 +2935,17 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2875,7 +2955,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2887,7 +2967,7 @@
       <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2898,19 +2978,23 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>PL Scorer</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr"/>
+          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -2924,12 +3008,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2939,7 +3023,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2951,7 +3035,7 @@
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2962,21 +3046,21 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>4 Completions</t>
+          <t>Top Scorer</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
+          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2992,12 +3076,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3007,7 +3091,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3019,7 +3103,7 @@
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3030,21 +3114,21 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>3 Completions</t>
+          <t>Assister</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
+          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+          <t>1,750 Coins / Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -3060,12 +3144,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -3075,7 +3159,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -3087,7 +3171,7 @@
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3098,21 +3182,21 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2 Completions</t>
+          <t>Assist 3</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
+          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,000 Coins</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3128,12 +3212,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3143,7 +3227,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3155,7 +3239,7 @@
       <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -3166,21 +3250,21 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>1 Completion</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
+          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>2,000 Coins</t>
+          <t>Consumables Pack / 750 Coins / Consumable</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3196,12 +3280,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -3211,7 +3295,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -3223,7 +3307,7 @@
       <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3238,17 +3322,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Score in 9</t>
+          <t>Assist in 3</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3264,12 +3348,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3279,7 +3363,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3291,7 +3375,7 @@
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3302,24 +3386,28 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Win 1 match in any Football Ultimate Team game mode.</t>
+          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
+          <t>Consumables Pack / 500 Coins / Consumable</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -3328,30 +3416,34 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
       <c r="M24" s="3" t="inlineStr"/>
       <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3362,24 +3454,24 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Barbecue Sauce</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from each of the Premier League and Women's Super League in your starting 11.</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Stadium Tifo / Stadium Background Tifo</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
+          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -3388,30 +3480,34 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from each of the premier league and women's super league in your starting 11.||barbecue sauce</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3422,24 +3518,28 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Be a Goldfish</t>
+          <t>4 Completions</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
+          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -3448,30 +3548,34 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3482,24 +3586,28 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Unselfish Play</t>
+          <t>3 Completions</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr"/>
+          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -3508,30 +3616,34 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
       <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3542,24 +3654,28 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Football is Life</t>
+          <t>2 Completions</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in any Football Ultimate Team game mode.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr"/>
+          <t>4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -3568,30 +3684,34 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
       <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3602,19 +3722,23 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>1 Completion</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2,000 Coins</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -3628,12 +3752,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3643,7 +3767,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -3655,7 +3779,7 @@
       <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -3666,21 +3790,21 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Score in 30</t>
+          <t>Score in 9</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3696,12 +3820,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3711,7 +3835,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3723,7 +3847,7 @@
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3734,23 +3858,19 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Score in 20</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
-        </is>
-      </c>
+          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -3791,7 +3911,7 @@
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3802,21 +3922,21 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Assist 20</t>
+          <t>Score in 30</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3859,7 +3979,7 @@
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3870,21 +3990,21 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Assist 15</t>
+          <t>Score in 20</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -3927,7 +4047,7 @@
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -3938,21 +4058,21 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Assist 20</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
+          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3995,7 +4115,7 @@
       <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4006,21 +4126,21 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Assist 15</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
+          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4063,7 +4183,7 @@
       <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4074,21 +4194,21 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / Consumable</t>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4131,7 +4251,7 @@
       <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4142,26 +4262,26 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable.</t>
+          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>2X 84+ Gold Players Pack</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Watch / FC Pro</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
@@ -4172,12 +4292,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4187,27 +4307,19 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points and pack rewards! all rewards are untradeable.||weekly rush points - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -4218,26 +4330,26 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>35,000 Rush Points</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Earn 35,000 points by completing bonuses in Rush.</t>
+          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x 2x 84+ Gold Players Pack / 83+ Gold Player Pack</t>
+          <t>Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Watch / FC Pro</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
@@ -4248,12 +4360,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4263,27 +4375,19 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -4294,28 +4398,24 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>25,000 Rush Points</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Earn 25,000 points by completing bonuses in Rush.</t>
+          <t>Win 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>83+ Gold Player Pack / 2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -4329,37 +4429,25 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4370,28 +4458,24 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>20,000 Rush Points</t>
+          <t>Barbecue Sauce</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Earn 20,000 points by completing bonuses in Rush.</t>
+          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Stadium Tifo / Stadium Background Tifo</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -4405,37 +4489,25 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 20,000 points by completing bonuses in rush.||20,000 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from any premier league team and 1 player from any women's super league team in your starting 11.||barbecue sauce</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4446,28 +4518,24 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>10,000 Rush Points</t>
+          <t>Be a Goldfish</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Earn 10,000 points by completing bonuses in Rush.</t>
+          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -4481,37 +4549,25 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -4522,28 +4578,24 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2,500 Rush Points</t>
+          <t>Unselfish Play</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Earn 2,500 points by completing bonuses in Rush.</t>
+          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -4557,37 +4609,25 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4598,38 +4638,38 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Football is Life</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Play 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Large Gold Pack</t>
+          <t>Badge</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -4639,7 +4679,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr"/>
@@ -4647,7 +4687,7 @@
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -4658,28 +4698,32 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+          <t>2X 84+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -4689,25 +4733,37 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points and pack rewards! all rewards are untradeable.||weekly rush points - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4718,28 +4774,32 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>35,000 Rush Points</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>Earn 35,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x 2x 84+ Gold Players Pack / 83+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -4749,25 +4809,37 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -4778,28 +4850,32 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>25,000 Rush Points</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>Earn 25,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
+          <t>83+ Gold Player Pack / 2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -4809,25 +4885,37 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -4838,24 +4926,28 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>20,000 Rush Points</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Draft matches.</t>
+          <t>Earn 20,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
+          <t>2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -4864,30 +4956,42 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 20,000 points by completing bonuses in rush.||20,000 rush points</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -4898,24 +5002,28 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>10,000 Rush Points</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Draft matches.</t>
+          <t>Earn 10,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
+          <t>2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -4924,30 +5032,42 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -4958,24 +5078,28 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>2,500 Rush Points</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Draft matches.</t>
+          <t>Earn 2,500 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -4984,30 +5108,42 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5022,34 +5158,34 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Play 50</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Play 50 Co-Op matches.</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
+          <t>Large Gold Pack</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5059,7 +5195,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr"/>
@@ -5067,7 +5203,7 @@
       <c r="N50" s="3" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -5082,34 +5218,34 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Co-Op matches.</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5119,7 +5255,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr"/>
@@ -5127,7 +5263,7 @@
       <c r="N51" s="3" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -5142,34 +5278,34 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Co-Op matches.</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5179,7 +5315,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr"/>
@@ -5187,7 +5323,7 @@
       <c r="N52" s="3" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5198,42 +5334,38 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Score 20</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Score 20 goals as a team in Rush.</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5243,7 +5375,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr"/>
@@ -5251,7 +5383,7 @@
       <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -5262,28 +5394,24 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Bonuses</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Rush bonuses.</t>
+          <t>Play 15 Draft matches.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -5292,12 +5420,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5307,7 +5435,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr"/>
@@ -5315,7 +5443,7 @@
       <c r="N54" s="3" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -5326,28 +5454,24 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Bonuses</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Rush bonuses.</t>
+          <t>Play 10 Draft matches.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -5356,12 +5480,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5371,7 +5495,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr"/>
@@ -5379,7 +5503,7 @@
       <c r="N55" s="3" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -5390,28 +5514,24 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rush matches.</t>
+          <t>Play 5 Draft matches.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -5420,12 +5540,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -5435,7 +5555,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr"/>
@@ -5443,7 +5563,7 @@
       <c r="N56" s="3" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -5454,28 +5574,24 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 50</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rush matches.</t>
+          <t>Play 50 Co-Op matches.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -5489,7 +5605,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -5499,7 +5615,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr"/>
@@ -5507,7 +5623,7 @@
       <c r="N57" s="3" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -5518,28 +5634,24 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush matches.</t>
+          <t>Play 10 Co-Op matches.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -5553,7 +5665,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -5563,7 +5675,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr"/>
@@ -5571,7 +5683,7 @@
       <c r="N58" s="3" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -5582,38 +5694,38 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your foot</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
+          <t>Play 5 Co-Op matches.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 5,000 Coins</t>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -5623,7 +5735,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr"/>
@@ -5631,7 +5743,7 @@
       <c r="N59" s="3" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -5642,28 +5754,32 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Score 20</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Score 20 goals as a team in Rush.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr"/>
+          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -5673,7 +5789,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -5683,7 +5799,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr"/>
@@ -5691,7 +5807,7 @@
       <c r="N60" s="3" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -5702,28 +5818,32 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Complete 20 Bonuses</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Complete 20 Rush bonuses.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr"/>
+          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -5733,7 +5853,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -5743,7 +5863,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr"/>
@@ -5751,7 +5871,7 @@
       <c r="N61" s="3" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -5762,28 +5882,32 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Complete 10 Bonuses</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Complete 10 Rush bonuses.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
+          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -5793,7 +5917,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -5803,7 +5927,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr"/>
@@ -5811,7 +5935,7 @@
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -5822,26 +5946,26 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Get acquainted with Live Events matches.</t>
+          <t>Play 15 Rush matches.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick</t>
+          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr"/>
@@ -5852,12 +5976,12 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -5867,7 +5991,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr"/>
@@ -5875,7 +5999,7 @@
       <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
@@ -5886,26 +6010,26 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Play 20</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Play 20 Live Events matches.</t>
+          <t>Play 10 Rush matches.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr"/>
@@ -5916,12 +6040,12 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -5931,7 +6055,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr"/>
@@ -5939,7 +6063,7 @@
       <c r="N64" s="3" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -5950,26 +6074,26 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Live Events matches.</t>
+          <t>Play 5 Rush matches.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+          <t>1 Of 2 78+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr"/>
@@ -5980,12 +6104,12 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -5995,7 +6119,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr"/>
@@ -6003,7 +6127,7 @@
       <c r="N65" s="3" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -6014,42 +6138,38 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete Moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Live Events matches.</t>
+          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Coin Boost / 5,000 Coins</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -6059,7 +6179,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr"/>
@@ -6067,7 +6187,7 @@
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -6078,42 +6198,38 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Squad Battles Matches on any difficulty.</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -6123,7 +6239,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr"/>
@@ -6131,7 +6247,7 @@
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -6142,42 +6258,38 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Squad Battles Matches on any difficulty.</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -6187,7 +6299,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr"/>
@@ -6195,7 +6307,7 @@
       <c r="N68" s="3" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
@@ -6206,42 +6318,38 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles Matches on any difficulty.</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -6251,7 +6359,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr"/>
@@ -6259,7 +6367,7 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -6274,22 +6382,22 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rivals matches.</t>
+          <t>Get acquainted with Live Events matches.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
+          <t>1 Of 2 80+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr"/>
@@ -6300,12 +6408,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -6315,7 +6423,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr"/>
@@ -6323,7 +6431,7 @@
       <c r="N70" s="3" t="inlineStr"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
@@ -6338,22 +6446,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 20</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rivals matches.</t>
+          <t>Play 20 Live Events matches.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr"/>
@@ -6364,12 +6472,12 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -6379,7 +6487,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr"/>
@@ -6387,7 +6495,7 @@
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -6402,22 +6510,22 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals matches.</t>
+          <t>Play 10 Live Events matches.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr"/>
@@ -6428,12 +6536,12 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -6443,7 +6551,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -6451,7 +6559,7 @@
       <c r="N72" s="3" t="inlineStr"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
@@ -6462,26 +6570,26 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Champions matches.</t>
+          <t>Play 5 Live Events matches.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr"/>
@@ -6492,12 +6600,12 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -6507,7 +6615,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr"/>
@@ -6515,7 +6623,7 @@
       <c r="N73" s="3" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -6526,26 +6634,26 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Champions matches.</t>
+          <t>Play 15 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Squad Battles</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr"/>
@@ -6556,12 +6664,12 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -6571,7 +6679,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -6579,7 +6687,7 @@
       <c r="N74" s="3" t="inlineStr"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -6590,26 +6698,26 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions matches.</t>
+          <t>Play 10 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>75-83 Gold Player Pack / Coin Boost</t>
+          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Squad Battles</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr"/>
@@ -6620,12 +6728,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -6635,7 +6743,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr"/>
@@ -6643,7 +6751,7 @@
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
@@ -6654,24 +6762,28 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Scoring Success</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals in any FUT game mode.</t>
+          <t>Play 5 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>10 SP</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr"/>
+          <t>75+ Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
@@ -6680,42 +6792,30 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>G025</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N76" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/||score 2 goals in any fut game mode.||scoring success</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -6730,20 +6830,24 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Score 10 goals in any FUT game mode using an English player.</t>
+          <t>Play 15 Rivals matches.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>500 SP / 50 SP</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr"/>
+          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -6752,42 +6856,30 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N77" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -6802,29 +6894,25 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+          <t>Play 10 Rivals matches.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>Rivals</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -6832,42 +6920,30 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N78" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -6882,22 +6958,22 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
+          <t>Play 5 Rivals matches.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Rush</t>
+          <t>Rivals</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr"/>
@@ -6908,52 +6984,532 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Play 15</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Play 15 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>G024</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>G024</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>G024</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr"/>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Scoring Success</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Score 2 goals in any FUT game mode.</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>10 SP</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
           <t>G026</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/||score 2 goals in any fut game mode.||scoring success</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Score 10</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Score 10 goals in any FUT game mode using an English player.</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>500 SP / 50 SP</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr">
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
         </is>
       </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr">
+      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
-      <c r="O79" s="3" t="inlineStr">
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Win 10</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Rush</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
         </is>
       </c>
-      <c r="P79" s="3" t="inlineStr">
+      <c r="P86" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P79"/>
+  <autoFilter ref="A1:P86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6964,7 +7520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -7016,7 +7572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7026,100 +7582,96 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points</t>
+          <t>NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 85% 15%</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 3 days</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>9/20 02:00</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-20T02:00+09:00</t>
-        </is>
-      </c>
+          <t>NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 98% 2%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack</t>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 13 days 2 Objectives 52% 48%</t>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 2 days 3 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>9/20 02:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-09-20T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack</t>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0%</t>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 12 days 2 Objectives 63% 37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Expires in 12 days</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -7129,12 +7681,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack</t>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 76% 24%</t>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7148,7 +7700,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7158,12 +7710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack</t>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 77% 23%</t>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7177,7 +7729,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -7187,12 +7739,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack</t>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 78% 22%</t>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7206,7 +7758,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7216,12 +7768,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack</t>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 78% 22%</t>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7235,7 +7787,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -7245,12 +7797,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho</t>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 98% 3%</t>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7264,7 +7816,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7274,12 +7826,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande</t>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 96% 4%</t>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7293,7 +7845,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -7303,12 +7855,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0%</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 97% 3%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7322,25 +7874,29 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 100% 0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 month</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -7362,7 +7918,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 97% 3%</t>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7376,69 +7932,69 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack</t>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 86% 14%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 97% 3%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9%</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 5 days 5 Objectives 91% 9%</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9/23 02:00</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7448,12 +8004,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone Draft your path to greatness! Large Gold Pack</t>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8%</t>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -7463,7 +8019,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -7473,12 +8029,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins</t>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 79% 21%</t>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -7488,7 +8044,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7498,12 +8054,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost</t>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 92% 8%</t>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -7513,7 +8069,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -7523,12 +8079,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins</t>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17%</t>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -7538,7 +8094,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -7548,12 +8104,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost</t>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 90% 10%</t>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 88% 13%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -7563,7 +8119,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -7573,12 +8129,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick</t>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9%</t>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -7588,7 +8144,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -7598,12 +8154,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack</t>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10%</t>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -7613,7 +8169,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -7623,12 +8179,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack</t>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10%</t>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -7638,7 +8194,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -7648,12 +8204,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins</t>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11%</t>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -7663,7 +8219,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -7673,12 +8229,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock</t>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 83% 17%</t>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -7688,79 +8244,104 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP</t>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 15 days 30 total 2 Objectives 100% 0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 88% 12%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 14 days 30 total 2 Objectives 91% 9%</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 15 days 500 total 5 Objectives 100% 0%</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 15 days</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 14 days 500 total 5 Objectives 100% 0%</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 14 days</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:G28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7771,7 +8352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7805,555 +8386,599 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 13 days 2 Objectives 52% 48% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 98% 2% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 2 days 3 Objectives 90% 10% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 76% 24% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 12 days 2 Objectives 63% 37% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 77% 23% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 96% 4% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 78% 22% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 78% 22% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 98% 3% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 96% 4% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 85% 15% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 100% 0% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from each of the Premier League and Women's Super League in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 97% 3% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 97% 3% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 86% 14% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 95% 5% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 97% 3% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 5 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 79% 21% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 90% 10% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 88% 13% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 94% 6% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 83% 17% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 93% 7% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>G025</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 15 days 30 total 2 Objectives 100% 0% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 92% 8% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>G025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 88% 12% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>G026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 14 days 30 total 2 Objectives 91% 9% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 15 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 14 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8364,7 +8989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8386,22 +9011,19 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TimeoutError: Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/", waiting until "networkidle"
-</t>
+          <t>No objective text extracted</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -8410,20 +9032,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>No objective text extracted</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -17,11 +17,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manifest'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'How_To_Read'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 05:01:17</t>
+          <t>2026-09-24 04:59:59</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 02:00:00</t>
+          <t>2026-09-24 02:00:00</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -646,30 +646,42 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>9/26 02:00</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 98% 2% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Tactical Trials Tactical Trials - EA SPORTS FC 27 Objectives Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa Expires in 2 days 4 Objectives 77% 23% Rewards 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack Win 3 Win 3 matches using only the 3-4-2-1 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Premier League in your starting 11. 2X 81+ Gold Players Pack Score 6 Score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the LALIGA in your starting 11. 2X 80+ Gold Players Pack Score 4 Score 4 goals using only the 5-2-1-2 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Bundesliga in your starting 11. 2X 78+ Gold Players Pack Play 5 Play 5 matches using only the 4-3-3 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Eredivisie in your starting 11. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -684,7 +696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -699,27 +711,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>9/20 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 2 days 3 Objectives 90% 10% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 65% 35% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -734,12 +746,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -749,27 +761,27 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>10/5 02:00</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-10-05T02:00+09:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 12 days 2 Objectives 63% 37% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 11 days 2 Objectives 11% 89% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -778,18 +790,18 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -799,19 +811,15 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 96% 4% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 95% 5% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -826,34 +834,42 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 6 days 2 Objectives 61% 39% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -862,18 +878,18 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -883,19 +899,27 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 28 days 1 Objectives 92% 8% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -904,18 +928,18 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -925,19 +949,27 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 28 days 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -946,18 +978,18 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -967,19 +999,27 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 85% 15% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 28 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -988,18 +1028,18 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1009,19 +1049,27 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 28 days 4 Objectives 87% 13% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1036,12 +1084,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1051,19 +1099,27 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 97% 3% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 28 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1072,18 +1128,18 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1093,19 +1149,27 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 28 days 4 Objectives 93% 8% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1114,18 +1178,18 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1135,19 +1199,27 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 95% 5% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 28 days 4 Objectives 93% 7% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1156,36 +1228,48 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 97% 3% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 28 days 4 Objectives 93% 7% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1200,12 +1284,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1215,27 +1299,27 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 28 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>9/23 02:00</t>
+          <t>10/22 02:00</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23T02:00+09:00</t>
+          <t>2026-10-22T02:00+09:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 5 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 28 days 7 Objectives 91% 9% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1244,18 +1328,18 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1265,7 +1349,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
@@ -1273,7 +1357,7 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1282,13 +1366,13 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1311,7 +1395,7 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1326,7 +1410,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1364,7 +1448,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1387,7 +1471,7 @@
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 89% 11% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1402,7 +1486,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1425,7 +1509,7 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 88% 13% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1438,90 +1522,90 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>G020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>G021</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 90% 10% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>G022</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 94% 6% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 92% 8% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>G021</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1531,7 +1615,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
@@ -1539,7 +1623,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1548,18 +1632,18 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1569,7 +1653,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
@@ -1577,7 +1661,7 @@
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 93% 7% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1592,12 +1676,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G025</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1607,7 +1691,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
@@ -1615,7 +1699,7 @@
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 92% 8% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1628,97 +1712,85 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>G025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 88% 12% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 78% 22% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J27" s="2" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>G026</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Seasonal</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 14 days</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 14 days 30 total 2 Objectives 91% 9% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>G027</t>
+          <t>G028</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1738,7 +1810,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1753,7 +1825,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 14 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 8 days 500 total 5 Objectives 91% 9% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1765,8 +1837,58 @@
         <v>3</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>G029</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 8 days</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 8 days 30 total 2 Objectives 92% 8% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1777,7 +1899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1886,52 +2008,64 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband</t>
+          <t>Win 3 matches using only the 3-4-2-1 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Premier League in your starting 11.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+          <t>1x 2x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 2X 81+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>9/26 02:00</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband||claim the armband</t>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||win 3 matches using only the 3-4-2-1 formation (without changing) in any football ultimate team game mode while having min. 1 player from the premier league in your starting 11.||win 3</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -1946,52 +2080,64 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Score 6</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the LALIGA in your starting 11.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>9/26 02:00</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband - ea sports fc 27 objectives||claim the armband - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any football ultimate team game mode while having min. 1 player from the laliga in your starting 11.||score 6</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -2006,52 +2152,64 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Score 4</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Score 4 goals using only the 5-2-1-2 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Bundesliga in your starting 11.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+          <t>2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>9/26 02:00</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play 1||play 1</t>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||score 4 goals using only the 5-2-1-2 formation (without changing) in any football ultimate team game mode while having min. 1 player from the bundesliga in your starting 11.||score 4</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -2066,52 +2224,64 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Play a match in any FUT game mode.</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Play a match in any FUT game mode.</t>
+          <t>Play 5 matches using only the 4-3-3 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Eredivisie in your starting 11.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>9/26 02:00</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play a match in any fut game mode.||play a match in any fut game mode.</t>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||play 5 matches using only the 4-3-3 (2) formation (without changing) in any football ultimate team game mode while having min. 1 player from the eredivisie in your starting 11.||play 5</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -2152,7 +2322,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -2167,27 +2337,27 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>9/20 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/||win 15 matches in squad battles on min. world class difficulty.||win 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 15 matches in squad battles on min. world class difficulty.||win 15</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -2228,7 +2398,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -2243,27 +2413,27 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>9/20 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/||win 12 matches in squad battles on min. world class difficulty.||win 12</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 12 matches in squad battles on min. world class difficulty.||win 12</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -2304,7 +2474,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -2319,27 +2489,27 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>9/20 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/||win 10 matches in squad battles on min. world class difficulty.||win 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 10 matches in squad battles on min. world class difficulty.||win 10</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -2354,17 +2524,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Hit the Pitch</t>
+          <t>Compete</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Play 5 matches in the FC Pro Open Ladder.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
+          <t>Badge</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2380,12 +2550,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2395,27 +2565,27 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>10/5 02:00</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-10-05T02:00+09:00</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/||play 5 matches in the fc pro open ladder.||compete</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -2426,72 +2596,56 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Kick Off</t>
+          <t>Claim the Armband</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Claim the Armband</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 12 days</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>9/30 02:00</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband||claim the armband</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -2502,28 +2656,24 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -2532,12 +2682,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2547,19 +2697,15 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband - ea sports fc 27 objectives||claim the armband - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -2570,28 +2716,24 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective.</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -2600,12 +2742,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -2615,19 +2757,15 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play 1||play 1</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -2638,28 +2776,24 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objective.</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -2668,12 +2802,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2683,19 +2817,15 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play a match in any fut game mode.||play a match in any fut game mode.</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -2706,21 +2836,21 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Hit the Pitch</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,500 Coins</t>
+          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2731,39 +2861,47 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2774,21 +2912,21 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The Final Challenge</t>
+          <t>Kick Off</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
+          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2804,34 +2942,42 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2846,17 +2992,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Finesse</t>
+          <t>Score in 9</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
+          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / Consumable / 1,500 Coins</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2872,12 +3018,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2887,19 +3033,27 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2910,21 +3064,21 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Serial Winner</t>
+          <t>The Final Challenge</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
+          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
+          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2940,12 +3094,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2955,19 +3109,27 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2978,21 +3140,21 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>PL Scorer</t>
+          <t>Finesse</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
+          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
+          <t>Evo Unlock / Consumable / 1,500 Coins</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -3008,7 +3170,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -3028,14 +3190,22 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -3046,21 +3216,21 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Top Scorer</t>
+          <t>Serial Winner</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
+          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3076,12 +3246,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3091,19 +3261,27 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3114,21 +3292,21 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Assister</t>
+          <t>PL Scorer</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
+          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>1,750 Coins / Consumables Pack / Consumable</t>
+          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -3144,12 +3322,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -3159,19 +3337,27 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3186,17 +3372,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Assist 3</t>
+          <t>Top Scorer</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
+          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3212,12 +3398,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3227,19 +3413,27 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -3254,17 +3448,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Assister</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 750 Coins / Consumable</t>
+          <t>1,750 Coins / Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3280,12 +3474,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -3295,19 +3489,27 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3322,17 +3524,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3</t>
+          <t>Assist 3</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3348,12 +3550,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3363,19 +3565,27 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3395,12 +3605,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 500 Coins / Consumable</t>
+          <t>Consumables Pack / 750 Coins / Consumable</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -3416,12 +3626,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3431,19 +3641,27 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3458,15 +3676,19 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Assist in 3</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
+          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -3480,12 +3702,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3495,19 +3717,27 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3522,17 +3752,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>4 Completions</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
+          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+          <t>Consumables Pack / 500 Coins / Consumable</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3548,12 +3778,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3563,19 +3793,27 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3586,21 +3824,21 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>3 Completions</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3611,17 +3849,17 @@
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3631,19 +3869,27 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3654,21 +3900,21 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2 Completions</t>
+          <t>Complete the Ones We Watched World Class Challenge objective</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
+          <t>Complete the Ones We Watched World Class Challenge objective.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,000 Coins</t>
+          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3679,17 +3925,17 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3699,19 +3945,27 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3722,21 +3976,21 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>1 Completion</t>
+          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
+          <t>Complete the Ones We Watched Professional Challenge objective.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2,000 Coins</t>
+          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -3747,17 +4001,17 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3767,19 +4021,27 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -3790,21 +4052,21 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Score in 9</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3815,17 +4077,17 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3835,19 +4097,27 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3862,12 +4132,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
+          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -3884,12 +4154,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3899,19 +4169,27 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3926,17 +4204,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Score in 30</t>
+          <t>4 Completions</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
+          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3952,12 +4230,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3967,19 +4245,27 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3994,17 +4280,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Score in 20</t>
+          <t>3 Completions</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
+          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4020,12 +4306,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -4035,19 +4321,27 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4062,17 +4356,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Assist 20</t>
+          <t>2 Completions</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
+          <t>4,000 Coins / 2,000 Coins</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4088,12 +4382,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4103,19 +4397,27 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4130,17 +4432,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Assist 15</t>
+          <t>1 Completion</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>2,000 Coins</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4156,12 +4458,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4171,19 +4473,27 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4194,23 +4504,19 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
-        </is>
-      </c>
+          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -4224,7 +4530,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -4244,14 +4550,22 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4262,21 +4576,21 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Score in 30</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4292,7 +4606,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -4312,14 +4626,22 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -4330,21 +4652,21 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Score in 20</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / Consumable</t>
+          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -4360,7 +4682,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -4380,14 +4702,22 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr"/>
-      <c r="N38" s="3" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -4398,24 +4728,28 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Assist 20</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Win 1 match in any Football Ultimate Team game mode.</t>
+          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
+          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -4424,30 +4758,42 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4458,24 +4804,28 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Barbecue Sauce</t>
+          <t>Assist 15</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11.</t>
+          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
+          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -4484,30 +4834,42 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from any premier league team and 1 player from any women's super league team in your starting 11.||barbecue sauce</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4518,24 +4880,28 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Be a Goldfish</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
+          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -4544,30 +4910,42 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -4578,24 +4956,28 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Unselfish Play</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
+          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -4604,30 +4986,42 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4638,24 +5032,28 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Football is Life</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in any Football Ultimate Team game mode.</t>
+          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
+          <t>Consumables Pack / Consumable</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -4664,30 +5062,42 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -4702,24 +5112,20 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable.</t>
+          <t>Win 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>2X 84+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -4728,42 +5134,30 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 5 days</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points and pack rewards! all rewards are untradeable.||weekly rush points - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4778,24 +5172,20 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>35,000 Rush Points</t>
+          <t>Barbecue Sauce</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Earn 35,000 points by completing bonuses in Rush.</t>
+          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x 2x 84+ Gold Players Pack / 83+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Stadium Tifo / Stadium Background Tifo</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -4804,42 +5194,30 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 5 days</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from any premier league team and 1 player from any women's super league team in your starting 11.||barbecue sauce</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -4854,24 +5232,20 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>25,000 Rush Points</t>
+          <t>Be a Goldfish</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Earn 25,000 points by completing bonuses in Rush.</t>
+          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>83+ Gold Player Pack / 2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -4880,42 +5254,30 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 5 days</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -4930,24 +5292,20 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>20,000 Rush Points</t>
+          <t>Unselfish Play</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Earn 20,000 points by completing bonuses in Rush.</t>
+          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -4956,42 +5314,30 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 5 days</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 20,000 points by completing bonuses in rush.||20,000 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -5006,24 +5352,20 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>10,000 Rush Points</t>
+          <t>Football is Life</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Earn 10,000 points by completing bonuses in Rush.</t>
+          <t>Play 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Badge</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -5032,42 +5374,30 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 5 days</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -5078,28 +5408,24 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>2,500 Rush Points</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Earn 2,500 points by completing bonuses in Rush.</t>
+          <t>Play 15 Draft matches.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -5108,42 +5434,30 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 5 days</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>9/23 02:00</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5154,38 +5468,38 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Play 10 Draft matches.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Large Gold Pack</t>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5195,7 +5509,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr"/>
@@ -5203,7 +5517,7 @@
       <c r="N50" s="3" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -5214,38 +5528,38 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Play 5 Draft matches.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5255,7 +5569,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr"/>
@@ -5263,7 +5577,7 @@
       <c r="N51" s="3" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -5274,38 +5588,38 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>Play 50</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>Play 50 Co-Op matches.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5315,7 +5629,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr"/>
@@ -5323,7 +5637,7 @@
       <c r="N52" s="3" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5334,38 +5648,38 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>Play 10 Co-Op matches.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5375,7 +5689,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr"/>
@@ -5383,7 +5697,7 @@
       <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -5394,21 +5708,21 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Draft matches.</t>
+          <t>Play 5 Co-Op matches.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr"/>
@@ -5420,12 +5734,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5435,7 +5749,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr"/>
@@ -5443,7 +5757,7 @@
       <c r="N54" s="3" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -5454,24 +5768,28 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Score 20</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Draft matches.</t>
+          <t>Score 20 goals as a team in Rush.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr"/>
+          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -5480,12 +5798,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5495,7 +5813,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr"/>
@@ -5503,7 +5821,7 @@
       <c r="N55" s="3" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -5514,24 +5832,28 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete 20 Bonuses</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Draft matches.</t>
+          <t>Complete 20 Rush bonuses.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr"/>
+          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -5540,12 +5862,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -5555,7 +5877,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr"/>
@@ -5563,7 +5885,7 @@
       <c r="N56" s="3" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -5574,24 +5896,28 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Play 50</t>
+          <t>Complete 10 Bonuses</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Play 50 Co-Op matches.</t>
+          <t>Complete 10 Rush bonuses.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr"/>
+          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -5600,12 +5926,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -5615,7 +5941,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr"/>
@@ -5623,7 +5949,7 @@
       <c r="N57" s="3" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -5634,24 +5960,28 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Co-Op matches.</t>
+          <t>Play 15 Rush matches.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr"/>
+          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -5660,12 +5990,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -5675,7 +6005,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr"/>
@@ -5683,7 +6013,7 @@
       <c r="N58" s="3" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -5694,24 +6024,28 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Co-Op matches.</t>
+          <t>Play 10 Rush matches.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr"/>
+          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -5720,12 +6054,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -5735,7 +6069,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr"/>
@@ -5743,7 +6077,7 @@
       <c r="N59" s="3" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -5754,21 +6088,21 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Score 20</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Score 20 goals as a team in Rush.</t>
+          <t>Play 5 Rush matches.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+          <t>1 Of 2 78+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -5784,7 +6118,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -5807,7 +6141,7 @@
       <c r="N60" s="3" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -5818,42 +6152,38 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Bonuses</t>
+          <t>Complete Moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Rush bonuses.</t>
+          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Coin Boost / 5,000 Coins</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -5863,7 +6193,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr"/>
@@ -5871,7 +6201,7 @@
       <c r="N61" s="3" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -5882,42 +6212,38 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Bonuses</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Rush bonuses.</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -5927,7 +6253,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr"/>
@@ -5935,7 +6261,7 @@
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -5946,42 +6272,38 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rush matches.</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -5991,7 +6313,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr"/>
@@ -5999,7 +6321,7 @@
       <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
@@ -6010,42 +6332,38 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rush matches.</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -6055,7 +6373,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr"/>
@@ -6063,7 +6381,7 @@
       <c r="N64" s="3" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -6074,42 +6392,38 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush matches.</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>Large Gold Pack</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -6119,7 +6433,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr"/>
@@ -6127,7 +6441,7 @@
       <c r="N65" s="3" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -6138,21 +6452,21 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your foot</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 5,000 Coins</t>
+          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr"/>
@@ -6164,12 +6478,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -6179,7 +6493,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr"/>
@@ -6187,7 +6501,7 @@
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -6198,21 +6512,21 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr"/>
@@ -6224,12 +6538,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -6239,7 +6553,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr"/>
@@ -6247,7 +6561,7 @@
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -6258,21 +6572,21 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr"/>
@@ -6284,12 +6598,12 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -6299,7 +6613,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr"/>
@@ -6307,7 +6621,7 @@
       <c r="N68" s="3" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
@@ -6318,38 +6632,42 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Get acquainted with Live Events matches.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr"/>
+          <t>1 Of 2 80+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Live Events</t>
+        </is>
+      </c>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -6359,7 +6677,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr"/>
@@ -6367,7 +6685,7 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -6378,21 +6696,21 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Play 20</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Get acquainted with Live Events matches.</t>
+          <t>Play 20 Live Events matches.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick</t>
+          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -6408,7 +6726,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -6431,7 +6749,7 @@
       <c r="N70" s="3" t="inlineStr"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
@@ -6442,21 +6760,21 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Play 20</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Play 20 Live Events matches.</t>
+          <t>Play 10 Live Events matches.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -6472,7 +6790,7 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -6495,7 +6813,7 @@
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -6506,21 +6824,21 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Live Events matches.</t>
+          <t>Play 5 Live Events matches.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -6536,7 +6854,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -6559,7 +6877,7 @@
       <c r="N72" s="3" t="inlineStr"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
@@ -6570,26 +6888,26 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Live Events matches.</t>
+          <t>Play 15 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Squad Battles</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr"/>
@@ -6600,12 +6918,12 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -6615,7 +6933,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr"/>
@@ -6623,7 +6941,7 @@
       <c r="N73" s="3" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -6634,21 +6952,21 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Squad Battles Matches on any difficulty.</t>
+          <t>Play 10 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -6664,7 +6982,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -6687,7 +7005,7 @@
       <c r="N74" s="3" t="inlineStr"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -6698,21 +7016,21 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Squad Battles Matches on any difficulty.</t>
+          <t>Play 5 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
+          <t>75+ Gold Player Pack / Coin Boost</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -6728,7 +7046,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -6751,7 +7069,7 @@
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
@@ -6762,26 +7080,26 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles Matches on any difficulty.</t>
+          <t>Play 15 Rivals matches.</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Coin Boost</t>
+          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
+          <t>Rivals</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr"/>
@@ -6792,12 +7110,12 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G025</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -6807,7 +7125,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -6815,7 +7133,7 @@
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -6826,21 +7144,21 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rivals matches.</t>
+          <t>Play 10 Rivals matches.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
+          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -6856,7 +7174,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G025</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -6879,7 +7197,7 @@
       <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -6890,21 +7208,21 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rivals matches.</t>
+          <t>Play 5 Rivals matches.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -6920,7 +7238,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G025</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -6943,7 +7261,7 @@
       <c r="N78" s="3" t="inlineStr"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -6954,26 +7272,26 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals matches.</t>
+          <t>Play 15 Champions matches.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Champions</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr"/>
@@ -6984,12 +7302,12 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -6999,7 +7317,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr"/>
@@ -7007,7 +7325,7 @@
       <c r="N79" s="3" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
@@ -7018,21 +7336,21 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Champions matches.</t>
+          <t>Play 10 Champions matches.</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
+          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -7048,7 +7366,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -7071,7 +7389,7 @@
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
@@ -7082,21 +7400,21 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Champions matches.</t>
+          <t>Play 5 Champions matches.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+          <t>75-83 Gold Player Pack / Coin Boost</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -7112,7 +7430,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -7135,7 +7453,7 @@
       <c r="N81" s="3" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
@@ -7146,28 +7464,24 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Score 10</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions matches.</t>
+          <t>Score 10 goals in any FUT game mode using an English player.</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>75-83 Gold Player Pack / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>Champions</t>
-        </is>
-      </c>
+          <t>500 SP / 50 SP</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
@@ -7176,30 +7490,42 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G028</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr"/>
-      <c r="M82" s="3" t="inlineStr"/>
-      <c r="N82" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 8 days</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
@@ -7210,25 +7536,33 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Scoring Success</t>
+          <t>Win 10</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals in any FUT game mode.</t>
+          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>10 SP</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="inlineStr"/>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -7236,12 +7570,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G028</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -7251,12 +7585,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -7271,7 +7605,7 @@
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/||score 2 goals in any fut game mode.||scoring success</t>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
@@ -7282,24 +7616,28 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Score 10 goals in any FUT game mode using an English player.</t>
+          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>500 SP / 50 SP</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr"/>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Rush</t>
+        </is>
+      </c>
       <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
@@ -7308,7 +7646,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>G027</t>
+          <t>G028</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -7328,7 +7666,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
@@ -7343,7 +7681,7 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -7354,33 +7692,25 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Scoring Success</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+          <t>Score 2 goals in any FUT game mode.</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>10 SP</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -7388,12 +7718,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>G027</t>
+          <t>G029</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -7403,12 +7733,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -7423,7 +7753,7 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/||score 2 goals in any fut game mode.||scoring success</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
@@ -7432,84 +7762,8 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Play 10</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles / Rivals / Rush</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>description_line_with_backward_title</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>G027</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>Seasonal</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 14 days</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N86" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
-      <c r="O86" s="3" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P86"/>
+  <autoFilter ref="A1:P85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7520,7 +7774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -7572,7 +7826,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7582,37 +7836,49 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick</t>
+          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 98% 2%</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 92% 8%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points</t>
+          <t>Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 2 days 3 Objectives 90% 10%</t>
+          <t>Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa Expires in 2 days 4 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7622,85 +7888,93 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>9/20 02:00</t>
+          <t>9/26 02:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T02:00+09:00</t>
+          <t>2026-09-26T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack</t>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 12 days 2 Objectives 63% 37%</t>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 65% 35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho</t>
+          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 96% 4%</t>
+          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 11 days 2 Objectives 11% 89%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>Expires in 11 days</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10/5 02:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7710,55 +7984,59 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack</t>
+          <t>Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 83% 17%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
+          <t>Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 95% 5%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack</t>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 83% 17%</t>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 6 days 2 Objectives 61% 39%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -7768,26 +8046,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 86% 14%</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 28 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -7797,26 +8083,34 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack</t>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 85% 15%</t>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 28 days 4 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7826,26 +8120,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack</t>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0%</t>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 28 days 4 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -7855,26 +8157,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande</t>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 97% 3%</t>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 28 days 4 Objectives 87% 13%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -7884,26 +8194,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable</t>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0%</t>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 28 days 4 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -7913,51 +8231,71 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville</t>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 95% 5%</t>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 28 days 4 Objectives 93% 8%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 month</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock</t>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 97% 3%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 28 days 4 Objectives 93% 7%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -7967,59 +8305,71 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 5 days 5 Objectives 91% 9%</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 28 days 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 28 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9/23 02:00</t>
+          <t>10/22 02:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T02:00+09:00</t>
+          <t>2026-10-22T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack</t>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 93% 7%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 28 days 7 Objectives 91% 9%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 28 days</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -8029,12 +8379,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone Draft your path to greatness! Large Gold Pack</t>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 94% 6%</t>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -8044,7 +8394,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -8054,12 +8404,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins</t>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17%</t>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -8069,7 +8419,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -8079,12 +8429,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost</t>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 94% 6%</t>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -8094,7 +8444,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8104,12 +8454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins</t>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 88% 13%</t>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -8119,7 +8469,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -8129,12 +8479,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost</t>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 94% 6%</t>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -8144,7 +8494,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8154,12 +8504,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick</t>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 93% 7%</t>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -8169,7 +8519,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -8179,12 +8529,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack</t>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8%</t>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -8194,7 +8544,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8204,12 +8554,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack</t>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 93% 7%</t>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -8219,7 +8569,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -8229,12 +8579,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins</t>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 92% 8%</t>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -8244,7 +8594,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8254,12 +8604,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock</t>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 88% 12%</t>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -8269,79 +8619,129 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP</t>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 14 days 30 total 2 Objectives 91% 9%</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 14 days</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11%</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 78% 22%</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 14 days 500 total 5 Objectives 100% 0%</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 14 days</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 8 days 500 total 5 Objectives 91% 9%</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 8 days</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 8 days 30 total 2 Objectives 92% 8%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 8 days</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G28"/>
+  <autoFilter ref="A1:G30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8352,7 +8752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8386,29 +8786,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. NEW Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 98% 2% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Tactical Trials Tactical Trials - EA SPORTS FC 27 Objectives Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa Expires in 2 days 4 Objectives 77% 23% Rewards 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack Win 3 Win 3 matches using only the 3-4-2-1 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Premier League in your starting 11. 2X 81+ Gold Players Pack Score 6 Score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the LALIGA in your starting 11. 2X 80+ Gold Players Pack Score 4 Score 4 goals using only the 5-2-1-2 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Bundesliga in your starting 11. 2X 78+ Gold Players Pack Play 5 Play 5 matches using only the 4-3-3 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Eredivisie in your starting 11. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -8418,305 +8818,305 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/92-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 2 days 3 Objectives 90% 10% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 65% 35% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 12 days 2 Objectives 63% 37% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 11 days 2 Objectives 11% 89% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 1 month 4 Objectives 96% 4% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 95% 5% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 6 days 2 Objectives 61% 39% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 1 month 4 Objectives 83% 17% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 28 days 1 Objectives 92% 8% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 1 month 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 28 days 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 1 month 4 Objectives 85% 15% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 28 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 1 month 4 Objectives 100% 0% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 28 days 4 Objectives 87% 13% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 1 month 4 Objectives 97% 3% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 28 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 1 month 1 Objectives 100% 0% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 28 days 4 Objectives 93% 8% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 1 month 7 Objectives 95% 5% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 28 days 4 Objectives 93% 7% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 97% 3% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 28 days 4 Objectives 93% 7% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/71-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 5 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 28 days 7 Objectives 91% 9% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -8731,14 +9131,14 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -8760,7 +9160,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -8775,14 +9175,14 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 94% 6% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 89% 11% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8797,168 +9197,168 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 88% 13% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 94% 6% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 90% 10% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 93% 7% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 92% 8% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 93% 7% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G025</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 92% 8% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>G025</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 88% 12% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G027</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 14 days 30 total 2 Objectives 91% 9% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 78% 22% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>G027</t>
+          <t>G028</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8973,12 +9373,34 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 14 days 500 total 5 Objectives 100% 0% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 8 days 500 total 5 Objectives 91% 9% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>G029</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 8 days 30 total 2 Objectives 92% 8% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:D29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8989,7 +9411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9011,29 +9433,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>No objective text extracted</t>
+          <t xml:space="preserve">TimeoutError: Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/", waiting until "networkidle"
+</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>No objective text extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>No objective text extracted</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -17,10 +17,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manifest'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'How_To_Read'!$A$1:$B$7</definedName>
   </definedNames>
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 04:59:59</t>
+          <t>2026-09-26 05:18:03</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 02:00:00</t>
+          <t>2026-09-26 02:00:00</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -646,12 +646,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -661,27 +661,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>9/26 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Tactical Trials Tactical Trials - EA SPORTS FC 27 Objectives Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa Expires in 2 days 4 Objectives 77% 23% Rewards 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack Win 3 Win 3 matches using only the 3-4-2-1 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Premier League in your starting 11. 2X 81+ Gold Players Pack Score 6 Score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the LALIGA in your starting 11. 2X 80+ Gold Players Pack Score 4 Score 4 goals using only the 5-2-1-2 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Bundesliga in your starting 11. 2X 78+ Gold Players Pack Play 5 Play 5 matches using only the 4-3-3 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Eredivisie in your starting 11. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP Expires in 7 days 200 total 5 Objectives 92% 8% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -696,42 +696,42 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 65% 35% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock Expires in 7 days 300 total 6 Objectives 78% 22% Rewards 300 SP 5,000 Coins Award Evo Unlock 1 Of 3 Destined For Glory W1 Loan Pick Evo Unlock 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. Evo Unlock 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -740,48 +740,36 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
+          <t>Gallery Foundations - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 11 days</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>10/5 02:00</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/123-gallery-foundations/</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 11 days 2 Objectives 11% 89% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 94% 6% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -796,12 +784,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -811,15 +799,27 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 4 days</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 95% 5% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 4 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -828,48 +828,48 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 6 days 2 Objectives 61% 39% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 1 day 3 Objectives 64% 36% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -878,48 +878,48 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 9 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>10/5 02:00</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-10-05T02:00+09:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 28 days 1 Objectives 92% 8% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 9 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -934,12 +934,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -949,27 +949,15 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 28 days</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>10/22 02:00</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 28 days 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 96% 4% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -978,48 +966,48 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 28 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 4 days 2 Objectives 56% 44% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1028,7 +1016,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1039,7 +1027,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1049,12 +1037,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1069,7 +1057,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 28 days 4 Objectives 87% 13% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 26 days 4 Objectives 81% 19% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1078,7 +1066,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1089,7 +1077,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1099,12 +1087,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1119,7 +1107,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 28 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 26 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1128,7 +1116,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1139,7 +1127,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1149,12 +1137,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1169,7 +1157,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 28 days 4 Objectives 93% 8% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 26 days 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1189,7 +1177,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1199,12 +1187,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1219,7 +1207,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 28 days 4 Objectives 93% 7% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 26 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1228,7 +1216,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1239,7 +1227,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1249,12 +1237,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1269,7 +1257,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 28 days 4 Objectives 93% 7% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 26 days 4 Objectives 93% 7% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1278,7 +1266,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1289,7 +1277,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1299,12 +1287,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1319,7 +1307,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 28 days 7 Objectives 91% 9% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 26 days 4 Objectives 91% 9% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1328,7 +1316,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1339,25 +1327,37 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 26 days 4 Objectives 90% 10% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1377,25 +1377,37 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 26 days 1 Objectives 85% 15% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1404,7 +1416,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1415,7 +1427,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1425,7 +1437,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr"/>
@@ -1433,7 +1445,7 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 95% 5% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1442,7 +1454,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1453,7 +1465,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1463,7 +1475,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
@@ -1471,7 +1483,7 @@
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 89% 11% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 91% 9% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1480,7 +1492,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1491,7 +1503,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1501,7 +1513,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
@@ -1509,7 +1521,7 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1518,7 +1530,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1529,7 +1541,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1539,7 +1551,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
@@ -1547,7 +1559,7 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 90% 10% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 81% 19% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1556,45 +1568,45 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>G022</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 92% 8% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>0</v>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 90% 10% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1605,7 +1617,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1615,7 +1627,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
@@ -1623,7 +1635,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 85% 15% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1643,7 +1655,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1653,7 +1665,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
@@ -1661,7 +1673,7 @@
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1670,45 +1682,45 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>G025</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>3</v>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 93% 7% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1719,7 +1731,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1729,7 +1741,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
@@ -1737,7 +1749,7 @@
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 92% 8% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1746,45 +1758,45 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 91% 9% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>G027</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 78% 22% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1795,37 +1807,25 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 8 days 500 total 5 Objectives 91% 9% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1838,57 +1838,145 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>G029</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 79% 21% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 6 days 500 total 5 Objectives 93% 7% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>G031</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 8 days 30 total 2 Objectives 92% 8% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="n">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 6 days 30 total 2 Objectives 93% 7% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1899,7 +1987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2008,17 +2096,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Winners Circle</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Win 3 matches using only the 3-4-2-1 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Premier League in your starting 11.</t>
+          <t>Win 7 matches in any FUT game mode.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 2X 81+ Gold Players Pack</t>
+          <t>1x 4x 82+ Gold Players Pack / 1x 4x 81+ Gold Players Pack / 1x 4x 80+ Gold Players Pack / 4X 83+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -2030,12 +2118,12 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -2045,27 +2133,27 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>9/26 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||win 3 matches using only the 3-4-2-1 formation (without changing) in any football ultimate team game mode while having min. 1 player from the premier league in your starting 11.||win 3</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/||win 7 matches in any fut game mode.||winners circle</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -2080,17 +2168,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Score 6</t>
+          <t>Wide Threat</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the LALIGA in your starting 11.</t>
+          <t>Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack</t>
+          <t>4X 83+ Gold Players Pack / 4X 82+ Gold Players Pack / 100 SP / EVO Ascension</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -2102,12 +2190,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -2117,27 +2205,27 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>9/26 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any football ultimate team game mode while having min. 1 player from the laliga in your starting 11.||score 6</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/||score at least 1 goal in 3 separate matches using a player with a preferred position of lm.||wide threat</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -2152,17 +2240,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Score 4</t>
+          <t>Smooth Samurai</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Score 4 goals using only the 5-2-1-2 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Bundesliga in your starting 11.</t>
+          <t>Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>EVO Ascension / Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. / 4X 81+ Gold Players Pack / 4X 80+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -2174,12 +2262,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2189,27 +2277,27 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>9/26 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||score 4 goals using only the 5-2-1-2 formation (without changing) in any football ultimate team game mode while having min. 1 player from the bundesliga in your starting 11.||score 4</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/||score at least 1 goal in 4 separate matches using a japanese player in any fut game mode.||smooth samurai</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -2224,17 +2312,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Composed Victory</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches using only the 4-3-3 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Eredivisie in your starting 11.</t>
+          <t>Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>4X 81+ Gold Players Pack / 4X 80+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -2246,12 +2334,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2261,27 +2349,27 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>9/26 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/||play 5 matches using only the 4-3-3 (2) formation (without changing) in any football ultimate team game mode while having min. 1 player from the eredivisie in your starting 11.||play 5</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/||win 3 matches in any fut game mode while having min. 2 players from eredivisie in your starting 11.||composed victory</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -2296,25 +2384,25 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Win 15</t>
+          <t>Score 1</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Win 15 matches in Squad Battles on min. World Class difficulty.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Evo Unlock / 1x 5x 78+ Gold Players Pack / 1x 10x 75+ Gold Players Pack / 5,000 Coins</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Min. World Class</t>
-        </is>
-      </c>
+          <t>Live Events / Destined for Glory Exhibition Live Event</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -2322,42 +2410,42 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 15 matches in squad battles on min. world class difficulty.||win 15</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/||score 1 goal from outside the box in the destined for glory exhibition live event.||score 1</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -2372,25 +2460,25 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Win 12</t>
+          <t>Score in 7</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Win 12 matches in Squad Battles on min. World Class difficulty.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
+          <t>Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5,000 Coins / 200 SP / 5X 78+ Gold Players Pack</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Min. World Class</t>
-        </is>
-      </c>
+          <t>Live Events / Destined for Glory Exhibition Live Event</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -2398,42 +2486,42 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 12 matches in squad battles on min. world class difficulty.||win 12</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/||score at least 1 goal in 7 separate matches in the destined for glory exhibition live event.||score in 7</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -2448,25 +2536,25 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Score 5</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on min. World Class difficulty.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
+          <t>Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>5X 78+ Gold Players Pack / 10X 75+ Gold Players Pack</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Min. World Class</t>
-        </is>
-      </c>
+          <t>Live Events / Destined for Glory Exhibition Live Event</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -2474,42 +2562,42 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 10 matches in squad battles on min. world class difficulty.||win 10</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/||score 5 low driven goals in the destined for glory exhibition live event.||score 5</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -2520,26 +2608,26 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Compete</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in the FC Pro Open Ladder.</t>
+          <t>Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Badge</t>
+          <t>10X 75+ Gold Players Pack / Evo Unlock / 100 SP</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
+          <t>Live Events / Destined for Glory Exhibition Live Event</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -2550,42 +2638,42 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 11 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>10/5 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/||play 5 matches in the fc pro open ladder.||compete</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/||win 3 matches in the destined for glory exhibition live event while having min. 2 french players in your starting 11.||win 3</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -2596,56 +2684,72 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband</t>
+          <t>Score in 3</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband</t>
+          <t>Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+          <t>10X 75+ Gold Players Pack / Evo Unlock / 100 SP / 1 Of 3 Destined For Glory W1 Loan Pick</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Destined for Glory Exhibition Live Event</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>10/3 02:00</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband||claim the armband</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/||score at least 1 goal in 3 separate matches in the destined for glory exhibition live event while having min. 1 destined for glory player in your starting 11.||score in 3</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -2656,56 +2760,72 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Play 1 match in the Destined for Glory Exhibition Live Event.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>Evo Unlock / 100 SP / 1 Of 3 Destined For Glory W1 Loan Pick</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Destined for Glory Exhibition Live Event</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>10/3 02:00</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband - ea sports fc 27 objectives||claim the armband - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/||play 1 match in the destined for glory exhibition live event.||play 1</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -2716,48 +2836,48 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Set in Motion</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Complete the Starter Set and get familiar with the Gallery.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+          <t>Small Silver Players Pack / Jumbo Bronze Pack / 250 Coins</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Gallery Foundations - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+          <t>https://www.fut.gg/objectives/milestones/123-gallery-foundations/</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
@@ -2765,7 +2885,7 @@
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play 1||play 1</t>
+          <t>https://www.fut.gg/objectives/milestones/123-gallery-foundations/||complete the starter set and get familiar with the gallery.||set in motion</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -2776,38 +2896,42 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Play a match in any FUT game mode.</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Play a match in any FUT game mode.</t>
+          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+          <t>2X 84+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2817,15 +2941,27 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 4 days</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play a match in any fut game mode.||play a match in any fut game mode.</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points and pack rewards! all rewards are untradeable.||weekly rush points - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -2836,26 +2972,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hit the Pitch</t>
+          <t>35,000 Rush Points</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Earn 35,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x 2x 84+ Gold Players Pack / 83+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -2866,27 +3002,27 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -2901,7 +3037,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2912,26 +3048,26 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Kick Off</t>
+          <t>25,000 Rush Points</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Earn 25,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
+          <t>83+ Gold Player Pack / 2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr"/>
@@ -2942,27 +3078,27 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2977,7 +3113,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2988,26 +3124,26 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Score in 9</t>
+          <t>20,000 Rush Points</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Earn 20,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>2X 82+ Gold Players Pack / 2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr"/>
@@ -3018,12 +3154,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -3033,27 +3169,27 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/||earn 20,000 points by completing bonuses in rush.||20,000 rush points</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -3064,26 +3200,26 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>The Final Challenge</t>
+          <t>10,000 Rush Points</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
+          <t>Earn 10,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
+          <t>2X 80+ Gold Players Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -3094,12 +3230,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -3109,27 +3245,27 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -3140,26 +3276,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Finesse</t>
+          <t>2,500 Rush Points</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
+          <t>Earn 2,500 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / Consumable / 1,500 Coins</t>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr"/>
@@ -3170,12 +3306,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -3185,27 +3321,27 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -3216,29 +3352,29 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Serial Winner</t>
+          <t>Win 15</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
+          <t>Win 15 matches in Squad Battles on min. World Class difficulty.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Min. World Class</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3246,12 +3382,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3261,27 +3397,27 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 15 matches in squad battles on min. world class difficulty.||win 15</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3292,29 +3428,29 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>PL Scorer</t>
+          <t>Win 12</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
+          <t>Win 12 matches in Squad Battles on min. World Class difficulty.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr"/>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Min. World Class</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3322,12 +3458,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -3337,27 +3473,27 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 12 matches in squad battles on min. world class difficulty.||win 12</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3368,29 +3504,29 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Top Scorer</t>
+          <t>Win 10</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
-        </is>
-      </c>
+          <t>Win 10 matches in Squad Battles on min. World Class difficulty.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Min. World Class</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3398,12 +3534,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3413,27 +3549,27 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/27 02:00</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-27T02:00+09:00</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 10 matches in squad battles on min. world class difficulty.||win 10</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -3444,21 +3580,21 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Assister</t>
+          <t>Compete</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
+          <t>Play 5 matches in the FC Pro Open Ladder.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>1,750 Coins / Consumables Pack / Consumable</t>
+          <t>Badge</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3474,42 +3610,42 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 9 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>10/5 02:00</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-10-05T02:00+09:00</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/||play 5 matches in the fc pro open ladder.||compete</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3524,38 +3660,34 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Assist 3</t>
+          <t>Claim the Armband</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Claim the Armband</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3565,27 +3697,15 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 28 days</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>10/22 02:00</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband||claim the armband</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3600,38 +3720,34 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 750 Coins / Consumable</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3641,27 +3757,15 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 28 days</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>10/22 02:00</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband - ea sports fc 27 objectives||claim the armband - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3672,42 +3776,38 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3717,27 +3817,15 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 28 days</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>10/22 02:00</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play 1||play 1</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3748,42 +3836,38 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 500 Coins / Consumable</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3793,27 +3877,15 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 28 days</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>10/22 02:00</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play a match in any fut game mode.||play a match in any fut game mode.</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3828,17 +3900,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Hit the Pitch</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
+          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3849,47 +3921,47 @@
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3904,17 +3976,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective</t>
+          <t>Kick Off</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective.</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
+          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3925,47 +3997,47 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3976,21 +4048,21 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
+          <t>The Final Challenge</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objective.</t>
+          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
+          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4001,17 +4073,17 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -4021,12 +4093,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4041,7 +4113,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4052,21 +4124,21 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Finesse</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,500 Coins</t>
+          <t>Evo Unlock / Consumable / 1,500 Coins</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4077,17 +4149,17 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -4097,12 +4169,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4117,7 +4189,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4128,19 +4200,23 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Serial Winner</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr"/>
+          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -4154,12 +4230,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -4169,12 +4245,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4189,7 +4265,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4200,21 +4276,21 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>4 Completions</t>
+          <t>PL Scorer</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
+          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4230,12 +4306,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4245,12 +4321,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -4265,7 +4341,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4276,21 +4352,21 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>3 Completions</t>
+          <t>Top Scorer</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
+          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4306,12 +4382,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -4321,12 +4397,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -4341,7 +4417,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4352,21 +4428,21 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2 Completions</t>
+          <t>Assister</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
+          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,000 Coins</t>
+          <t>1,750 Coins / Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4382,12 +4458,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4397,12 +4473,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -4417,7 +4493,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4428,21 +4504,21 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>1 Completion</t>
+          <t>Assist 3</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
+          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2,000 Coins</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4458,12 +4534,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4473,12 +4549,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -4493,7 +4569,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4504,19 +4580,23 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr"/>
+          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Consumables Pack / 750 Coins / Consumable</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -4530,12 +4610,12 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4545,12 +4625,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4565,7 +4645,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4576,21 +4656,21 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Score in 30</t>
+          <t>Assist in 3</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
+          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4606,12 +4686,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4621,12 +4701,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -4641,7 +4721,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -4652,21 +4732,21 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Score in 20</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
+          <t>Consumables Pack / 500 Coins / Consumable</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -4682,12 +4762,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4697,12 +4777,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4717,7 +4797,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -4728,21 +4808,21 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Assist 20</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
+          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4753,7 +4833,7 @@
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -4763,7 +4843,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4773,12 +4853,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -4793,7 +4873,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4804,21 +4884,21 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Assist 15</t>
+          <t>Complete the Ones We Watched World Class Challenge objective</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Ones We Watched World Class Challenge objective.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4829,7 +4909,7 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -4839,7 +4919,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4849,12 +4929,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4869,7 +4949,7 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4880,21 +4960,21 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Ones We Watched Professional Challenge objective.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
+          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4905,7 +4985,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -4915,7 +4995,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4925,12 +5005,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -4945,7 +5025,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -4956,21 +5036,21 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
+          <t>4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -4981,7 +5061,7 @@
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -4991,7 +5071,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5001,12 +5081,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5021,7 +5101,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5032,23 +5112,19 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Consumables Pack / Consumable</t>
-        </is>
-      </c>
+          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -5062,12 +5138,12 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5077,12 +5153,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5097,7 +5173,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5108,24 +5184,28 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>4 Completions</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Win 1 match in any Football Ultimate Team game mode.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -5139,25 +5219,37 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5168,24 +5260,28 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Barbecue Sauce</t>
+          <t>3 Completions</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
+          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -5199,25 +5295,37 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from any premier league team and 1 player from any women's super league team in your starting 11.||barbecue sauce</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5228,24 +5336,28 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Be a Goldfish</t>
+          <t>2 Completions</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
+          <t>4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -5259,25 +5371,37 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -5288,24 +5412,28 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Unselfish Play</t>
+          <t>1 Completion</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
+          <t>2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -5319,25 +5447,37 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -5348,24 +5488,28 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Football is Life</t>
+          <t>Score in 9</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in any Football Ultimate Team game mode.</t>
+          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -5374,30 +5518,42 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -5412,17 +5568,17 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Draft matches.</t>
+          <t>Win 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+          <t>Evo Unlock</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
@@ -5434,12 +5590,12 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5449,7 +5605,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr"/>
@@ -5457,7 +5613,7 @@
       <c r="N49" s="3" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5472,17 +5628,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Barbecue Sauce</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Draft matches.</t>
+          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+          <t>Stadium Tifo / Stadium Background Tifo</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
@@ -5494,12 +5650,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5509,7 +5665,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr"/>
@@ -5517,7 +5673,7 @@
       <c r="N50" s="3" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from any premier league team and 1 player from any women's super league team in your starting 11.||barbecue sauce</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -5532,17 +5688,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Be a Goldfish</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Draft matches.</t>
+          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr"/>
@@ -5554,12 +5710,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5569,7 +5725,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr"/>
@@ -5577,7 +5733,7 @@
       <c r="N51" s="3" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -5588,21 +5744,21 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Play 50</t>
+          <t>Unselfish Play</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Play 50 Co-Op matches.</t>
+          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
@@ -5619,7 +5775,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5629,7 +5785,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr"/>
@@ -5637,7 +5793,7 @@
       <c r="N52" s="3" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5648,21 +5804,21 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Football is Life</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Co-Op matches.</t>
+          <t>Play 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+          <t>Badge</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr"/>
@@ -5679,7 +5835,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5689,7 +5845,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr"/>
@@ -5697,7 +5853,7 @@
       <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -5708,24 +5864,28 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Co-Op matches.</t>
+          <t>Play 15 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr"/>
+          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -5734,12 +5894,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5749,7 +5909,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr"/>
@@ -5757,7 +5917,7 @@
       <c r="N54" s="3" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -5768,26 +5928,26 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Score 20</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Score 20 goals as a team in Rush.</t>
+          <t>Play 10 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Squad Battles</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
@@ -5803,7 +5963,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5813,7 +5973,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr"/>
@@ -5821,7 +5981,7 @@
       <c r="N55" s="3" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -5832,26 +5992,26 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Bonuses</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Rush bonuses.</t>
+          <t>Play 5 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
+          <t>75+ Gold Player Pack / Coin Boost</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Squad Battles</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr"/>
@@ -5867,7 +6027,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -5877,7 +6037,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr"/>
@@ -5885,7 +6045,7 @@
       <c r="N56" s="3" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -5896,28 +6056,24 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Bonuses</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Rush bonuses.</t>
+          <t>Play 15 Draft matches.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -5926,12 +6082,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -5941,7 +6097,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr"/>
@@ -5949,7 +6105,7 @@
       <c r="N57" s="3" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -5960,28 +6116,24 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rush matches.</t>
+          <t>Play 10 Draft matches.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -5990,12 +6142,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6005,7 +6157,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr"/>
@@ -6013,7 +6165,7 @@
       <c r="N58" s="3" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -6024,28 +6176,24 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rush matches.</t>
+          <t>Play 5 Draft matches.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -6054,12 +6202,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6069,7 +6217,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr"/>
@@ -6077,7 +6225,7 @@
       <c r="N59" s="3" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -6088,28 +6236,24 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 50</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush matches.</t>
+          <t>Play 50 Co-Op matches.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -6118,12 +6262,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -6133,7 +6277,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr"/>
@@ -6141,7 +6285,7 @@
       <c r="N60" s="3" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -6152,38 +6296,38 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your foot</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
+          <t>Play 10 Co-Op matches.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 5,000 Coins</t>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -6193,7 +6337,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr"/>
@@ -6201,7 +6345,7 @@
       <c r="N61" s="3" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -6212,38 +6356,38 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Play 5 Co-Op matches.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -6253,7 +6397,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr"/>
@@ -6261,7 +6405,7 @@
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -6272,38 +6416,42 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Score 20</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Score 20 goals as a team in Rush.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr"/>
+          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -6313,7 +6461,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr"/>
@@ -6321,7 +6469,7 @@
       <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
@@ -6332,38 +6480,42 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Complete 20 Bonuses</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Complete 20 Rush bonuses.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr"/>
+          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -6373,7 +6525,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr"/>
@@ -6381,7 +6533,7 @@
       <c r="N64" s="3" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -6392,38 +6544,42 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Complete 10 Bonuses</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Complete 10 Rush bonuses.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Large Gold Pack</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr"/>
+          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -6433,7 +6589,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr"/>
@@ -6441,7 +6597,7 @@
       <c r="N65" s="3" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -6452,38 +6608,42 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Play 15 Rush matches.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr"/>
+          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -6493,7 +6653,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr"/>
@@ -6501,7 +6661,7 @@
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -6512,38 +6672,42 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>Play 10 Rush matches.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr"/>
+          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -6553,7 +6717,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr"/>
@@ -6561,7 +6725,7 @@
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -6572,38 +6736,42 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>Play 5 Rush matches.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr"/>
+          <t>1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -6613,7 +6781,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr"/>
@@ -6621,7 +6789,7 @@
       <c r="N68" s="3" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
@@ -6636,28 +6804,24 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Complete Moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Get acquainted with Live Events matches.</t>
+          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Coin Boost / 5,000 Coins</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -6667,7 +6831,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -6677,7 +6841,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr"/>
@@ -6685,7 +6849,7 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -6700,28 +6864,24 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Play 20</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Play 20 Live Events matches.</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -6731,7 +6891,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -6741,7 +6901,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr"/>
@@ -6749,7 +6909,7 @@
       <c r="N70" s="3" t="inlineStr"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
@@ -6764,28 +6924,24 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Live Events matches.</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
@@ -6795,7 +6951,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -6805,7 +6961,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr"/>
@@ -6813,7 +6969,7 @@
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -6828,28 +6984,24 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Live Events matches.</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6859,7 +7011,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -6869,7 +7021,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -6877,7 +7029,7 @@
       <c r="N72" s="3" t="inlineStr"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
@@ -6892,28 +7044,24 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Squad Battles Matches on any difficulty.</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>Large Gold Pack</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -6923,7 +7071,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -6933,7 +7081,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr"/>
@@ -6941,7 +7089,7 @@
       <c r="N73" s="3" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -6956,28 +7104,24 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Squad Battles Matches on any difficulty.</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -6987,7 +7131,7 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -6997,7 +7141,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -7005,7 +7149,7 @@
       <c r="N74" s="3" t="inlineStr"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -7020,28 +7164,24 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles Matches on any difficulty.</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -7051,7 +7191,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -7061,7 +7201,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr"/>
@@ -7069,7 +7209,7 @@
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
@@ -7080,42 +7220,38 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rivals matches.</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>Rivals</t>
-        </is>
-      </c>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>G025</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -7125,7 +7261,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -7133,7 +7269,7 @@
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -7144,26 +7280,26 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rivals matches.</t>
+          <t>Get acquainted with Live Events matches.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+          <t>1 Of 2 80+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr"/>
@@ -7174,12 +7310,12 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>G025</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -7189,7 +7325,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr"/>
@@ -7197,7 +7333,7 @@
       <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -7208,26 +7344,26 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 20</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals matches.</t>
+          <t>Play 20 Live Events matches.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr"/>
@@ -7238,12 +7374,12 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>G025</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -7253,7 +7389,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -7261,7 +7397,7 @@
       <c r="N78" s="3" t="inlineStr"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -7272,26 +7408,26 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Champions matches.</t>
+          <t>Play 10 Live Events matches.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr"/>
@@ -7307,7 +7443,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -7317,7 +7453,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr"/>
@@ -7325,7 +7461,7 @@
       <c r="N79" s="3" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
@@ -7336,26 +7472,26 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Champions matches.</t>
+          <t>Play 5 Live Events matches.</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr"/>
@@ -7371,7 +7507,7 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -7381,7 +7517,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -7389,7 +7525,7 @@
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
@@ -7400,26 +7536,26 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions matches.</t>
+          <t>Play 15 Rivals matches.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>75-83 Gold Player Pack / Coin Boost</t>
+          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Rivals</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr"/>
@@ -7430,12 +7566,12 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G027</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -7445,7 +7581,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr"/>
@@ -7453,7 +7589,7 @@
       <c r="N81" s="3" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
@@ -7464,24 +7600,28 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Score 10 goals in any FUT game mode using an English player.</t>
+          <t>Play 10 Rivals matches.</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>500 SP / 50 SP</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr"/>
+          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
@@ -7490,42 +7630,30 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>G028</t>
+          <t>G027</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr"/>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
@@ -7536,33 +7664,29 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+          <t>Play 5 Rivals matches.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>Rivals</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -7570,42 +7694,30 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>G028</t>
+          <t>G027</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
+      <c r="N83" s="3" t="inlineStr"/>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
@@ -7616,26 +7728,26 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
+          <t>Play 15 Champions matches.</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Rush</t>
+          <t>Champions</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr"/>
@@ -7651,37 +7763,25 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr"/>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -7692,24 +7792,28 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Scoring Success</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals in any FUT game mode.</t>
+          <t>Play 10 Champions matches.</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>10 SP</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr"/>
+          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -7718,52 +7822,404 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>G029</t>
+          <t>G028</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="3" t="inlineStr"/>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>G028</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr"/>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Score 10</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Score 10 goals in any FUT game mode using an English player.</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>500 SP / 50 SP</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Win 10</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Rush</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Scoring Success</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Score 2 goals in any FUT game mode.</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>10 SP</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>G031</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
           <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="K85" s="3" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
         </is>
       </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="inlineStr">
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="N85" s="3" t="inlineStr">
+      <c r="N90" s="3" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
-      <c r="O85" s="3" t="inlineStr">
+      <c r="O90" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/||score 2 goals in any fut game mode.||scoring success</t>
         </is>
       </c>
-      <c r="P85" s="3" t="inlineStr">
+      <c r="P90" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P85"/>
+  <autoFilter ref="A1:P90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7774,7 +8230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -7826,155 +8282,143 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack</t>
+          <t>NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 6 days 5 Objectives 92% 8%</t>
+          <t>NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP Expires in 7 days 200 total 5 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa</t>
+          <t>NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa Expires in 2 days 4 Objectives 77% 23%</t>
+          <t>NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock Expires in 7 days 300 total 6 Objectives 78% 22%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>9/26 02:00</t>
+          <t>10/3 02:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T02:00+09:00</t>
+          <t>2026-10-03T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/milestones/123-gallery-foundations/</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points</t>
+          <t>NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 65% 35%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 3 days</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9/27 02:00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27T02:00+09:00</t>
-        </is>
-      </c>
+          <t>NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 94% 6%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 11 days 2 Objectives 11% 89%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 4 days 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 11 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10/5 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7984,22 +8428,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick</t>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 95% 5%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 1 day 3 Objectives 64% 36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 1 day</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9/27 02:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -8009,34 +8465,34 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack</t>
+          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 6 days 2 Objectives 61% 39%</t>
+          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 9 days 2 Objectives 10% 90%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 9 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>10/5 02:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-10-05T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -8046,71 +8502,59 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable</t>
+          <t>Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 28 days 1 Objectives 92% 8%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 28 days</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10/22 02:00</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 96% 4%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack</t>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 28 days 4 Objectives 83% 17%</t>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 4 days 2 Objectives 56% 44%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10/22 02:00</t>
+          <t>9/30 02:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T02:00+09:00</t>
+          <t>2026-09-30T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -8120,17 +8564,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack</t>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 28 days 4 Objectives 90% 10%</t>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 26 days 7 Objectives 87% 13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8147,7 +8591,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -8157,17 +8601,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack</t>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 28 days 4 Objectives 87% 13%</t>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 26 days 4 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8184,7 +8628,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -8194,17 +8638,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack</t>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 28 days 4 Objectives 91% 9%</t>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 26 days 4 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -8221,7 +8665,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -8231,17 +8675,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack</t>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 28 days 4 Objectives 93% 8%</t>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 26 days 4 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8258,7 +8702,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -8268,17 +8712,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho</t>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 28 days 4 Objectives 93% 7%</t>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 26 days 4 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8295,7 +8739,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -8305,17 +8749,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande</t>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 28 days 4 Objectives 93% 7%</t>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 26 days 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8332,7 +8776,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -8342,17 +8786,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville</t>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 28 days 7 Objectives 91% 9%</t>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 26 days 4 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 28 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8369,57 +8813,81 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6%</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 26 days 4 Objectives 90% 10%</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone Draft your path to greatness! Large Gold Pack</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 91% 9%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 26 days 1 Objectives 85% 15%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 26 days</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -8429,12 +8897,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins</t>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17%</t>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -8444,7 +8912,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8454,12 +8922,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost</t>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 89% 11%</t>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -8469,7 +8937,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -8479,12 +8947,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins</t>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17%</t>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -8494,7 +8962,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8504,12 +8972,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack</t>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 90% 10%</t>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -8519,7 +8987,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -8529,12 +8997,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost</t>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 92% 8%</t>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -8544,7 +9012,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8554,12 +9022,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick</t>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9%</t>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -8569,7 +9037,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -8579,12 +9047,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack</t>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10%</t>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -8594,7 +9062,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8604,12 +9072,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack</t>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10%</t>
+          <t>Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -8619,7 +9087,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -8629,12 +9097,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins</t>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11%</t>
+          <t>Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -8644,7 +9112,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8654,12 +9122,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock</t>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 78% 22%</t>
+          <t>Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -8669,79 +9137,129 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP</t>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 8 days 500 total 5 Objectives 91% 9%</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11%</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 79% 21%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 6 days 500 total 5 Objectives 93% 7%</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 8 days 30 total 2 Objectives 92% 8%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 6 days 30 total 2 Objectives 93% 7%</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:G32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8752,7 +9270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8786,176 +9304,176 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tactical Trials - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/91-tactical-trials/</t>
+          <t>https://www.fut.gg/objectives/campaigns/113-squad-foundations-shunsuke-mito/</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Tactical Trials Tactical Trials - EA SPORTS FC 27 Objectives Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Tactical Trials Show your strategic versatility to earn packs and Squad Foundations Lucas Rosa. All rewards are untradeable. Lucas Rosa Expires in 2 days 4 Objectives 77% 23% Rewards 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack Win 3 Win 3 matches using only the 3-4-2-1 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Premier League in your starting 11. 2X 81+ Gold Players Pack Score 6 Score 6 goals using only the 4-1-2-1-2 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the LALIGA in your starting 11. 2X 80+ Gold Players Pack Score 4 Score 4 goals using only the 5-2-1-2 formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Bundesliga in your starting 11. 2X 78+ Gold Players Pack Play 5 Play 5 matches using only the 4-3-3 (2) formation (without changing) in any Football Ultimate Team game mode while having min. 1 player from the Eredivisie in your starting 11. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP Expires in 7 days 200 total 5 Objectives 92% 8% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>Destined for Glory Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/109-destined-for-glory-exhibition/</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 3 days 3 Objectives 65% 35% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock Expires in 7 days 300 total 6 Objectives 78% 22% Rewards 300 SP 5,000 Coins Award Evo Unlock 1 Of 3 Destined For Glory W1 Loan Pick Evo Unlock 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. Evo Unlock 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
+          <t>Gallery Foundations - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
+          <t>https://www.fut.gg/objectives/milestones/123-gallery-foundations/</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 11 days 2 Objectives 11% 89% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 94% 6% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 95% 5% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 4 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 6 days 2 Objectives 61% 39% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 1 day 3 Objectives 64% 36% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 28 days 1 Objectives 92% 8% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 9 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 28 days 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 96% 4% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 28 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 4 days 2 Objectives 56% 44% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -8967,17 +9485,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 28 days 4 Objectives 87% 13% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 26 days 4 Objectives 81% 19% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -8989,17 +9507,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 28 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 26 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9011,17 +9529,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 28 days 4 Objectives 93% 8% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 26 days 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9033,17 +9551,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 28 days 4 Objectives 93% 7% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 26 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9055,17 +9573,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 28 days 4 Objectives 93% 7% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 26 days 4 Objectives 93% 7% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9077,17 +9595,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 28 days 7 Objectives 91% 9% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 26 days 4 Objectives 91% 9% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9099,17 +9617,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 26 days 4 Objectives 90% 10% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9121,17 +9639,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 26 days 1 Objectives 85% 15% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9143,17 +9661,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 95% 5% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9165,17 +9683,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 89% 11% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 91% 9% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9187,17 +9705,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 83% 17% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9209,17 +9727,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 90% 10% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 81% 19% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9231,17 +9749,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 92% 8% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 90% 10% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9253,17 +9771,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 85% 15% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9275,17 +9793,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 90% 10% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9297,17 +9815,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Transfer Market Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/47-transfer-market-milestone/</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 90% 10% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 93% 7% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9319,17 +9837,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 92% 8% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9341,17 +9859,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 78% 22% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 91% 9% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9363,17 +9881,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 8 days 500 total 5 Objectives 91% 9% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9385,22 +9903,66 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>Gallery Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/81-gallery-milestone/</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 79% 21% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 6 days 500 total 5 Objectives 93% 7% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>G031</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 8 days 30 total 2 Objectives 92% 8% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 6 days 30 total 2 Objectives 93% 7% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D29"/>
+  <autoFilter ref="A1:D31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9433,14 +9995,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TimeoutError: Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.fut.gg/objectives/seasonal/72-weekly-rush-points/", waiting until "networkidle"
+  - navigating to "https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manifest'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$4</definedName>
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 05:18:03</t>
+          <t>2026-09-27 04:34:28</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 02:00:00</t>
+          <t>2026-09-27 02:00:00</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -671,17 +671,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>10/3 02:00</t>
+          <t>10/4 02:00</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03T02:00+09:00</t>
+          <t>2026-10-04T02:00+09:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP Expires in 7 days 200 total 5 Objectives 92% 8% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. Shunsuke Mito 100 SP Expires in 7 days 200 total 5 Objectives 92% 8% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock Expires in 7 days 300 total 6 Objectives 78% 22% Rewards 300 SP 5,000 Coins Award Evo Unlock 1 Of 3 Destined For Glory W1 Loan Pick Evo Unlock 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. Evo Unlock 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Expires in 6 days 300 total 6 Objectives 79% 21% Rewards 300 SP 5,000 Coins Award 1 Of 3 Destined For Glory W1 Loan Pick 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 94% 6% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 90% 10% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 4 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 3 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -854,22 +854,22 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>9/27 13:00</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-09-27T13:00+09:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 1 day 3 Objectives 64% 36% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 11 hours 3 Objectives 64% 36% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 9 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 8 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 4 days 2 Objectives 56% 44% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 3 days 2 Objectives 57% 43% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1022,12 +1022,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 26 days 4 Objectives 81% 19% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 25 days 7 Objectives 87% 13% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 26 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 25 days 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1116,18 +1116,18 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 26 days 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 25 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 26 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 25 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 26 days 4 Objectives 93% 7% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 25 days 4 Objectives 94% 6% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 26 days 4 Objectives 91% 9% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 25 days 4 Objectives 92% 8% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 26 days 4 Objectives 90% 10% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 25 days 4 Objectives 89% 11% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 26 days 1 Objectives 85% 15% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 25 days 1 Objectives 86% 14% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 95% 5% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1483,7 +1483,7 @@
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 91% 9% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1521,7 +1521,7 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 93% 7% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1559,7 +1559,7 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 81% 19% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 82% 18% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1597,7 +1597,7 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 90% 10% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 91% 9% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1635,7 +1635,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 85% 15% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 86% 14% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1673,7 +1673,7 @@
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1863,7 +1863,7 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 79% 21% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 76% 24% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 6 days 500 total 5 Objectives 93% 7% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 5 days 500 total 5 Objectives 93% 7% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 6 days 30 total 2 Objectives 93% 7% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 5 days 30 total 2 Objectives 93% 7% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>10/3 02:00</t>
+          <t>10/4 02:00</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03T02:00+09:00</t>
+          <t>2026-10-04T02:00+09:00</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>10/3 02:00</t>
+          <t>10/4 02:00</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03T02:00+09:00</t>
+          <t>2026-10-04T02:00+09:00</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>10/3 02:00</t>
+          <t>10/4 02:00</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03T02:00+09:00</t>
+          <t>2026-10-04T02:00+09:00</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>10/3 02:00</t>
+          <t>10/4 02:00</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03T02:00+09:00</t>
+          <t>2026-10-04T02:00+09:00</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / 1x 5x 78+ Gold Players Pack / 1x 10x 75+ Gold Players Pack / 5,000 Coins</t>
+          <t>1 Of 3 Destined For Glory W1 Loan Pick / 1x 5x 78+ Gold Players Pack / 1x 10x 75+ Gold Players Pack / 5,000 Coins</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>10X 75+ Gold Players Pack / Evo Unlock / 100 SP</t>
+          <t>10X 75+ Gold Players Pack / 100 SP</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>10X 75+ Gold Players Pack / Evo Unlock / 100 SP / 1 Of 3 Destined For Glory W1 Loan Pick</t>
+          <t>10X 75+ Gold Players Pack / 100 SP / 1 Of 3 Destined For Glory W1 Loan Pick</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / 100 SP / 1 Of 3 Destined For Glory W1 Loan Pick</t>
+          <t>100 SP / 1 Of 3 Destined For Glory W1 Loan Pick</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>9/27 13:00</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-09-27T13:00+09:00</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3478,17 +3478,17 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>9/27 13:00</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-09-27T13:00+09:00</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3554,17 +3554,17 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>9/27 13:00</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-09-27T13:00+09:00</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4052,19 +4052,15 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>The Final Challenge</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
-        </is>
-      </c>
+          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -4078,12 +4074,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -4093,12 +4089,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4113,7 +4109,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4124,21 +4120,21 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Finesse</t>
+          <t>Score in 30</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
+          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / Consumable / 1,500 Coins</t>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4154,12 +4150,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -4169,12 +4165,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4189,7 +4185,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4200,21 +4196,21 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Serial Winner</t>
+          <t>Score in 20</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
+          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
+          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4230,12 +4226,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -4245,12 +4241,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4265,7 +4261,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4276,21 +4272,21 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PL Scorer</t>
+          <t>Assist 20</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
+          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
+          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4306,12 +4302,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4321,12 +4317,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -4341,7 +4337,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4352,21 +4348,21 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Top Scorer</t>
+          <t>Assist 15</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
+          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4382,12 +4378,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -4397,12 +4393,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -4417,7 +4413,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4428,21 +4424,21 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Assister</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
+          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>1,750 Coins / Consumables Pack / Consumable</t>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4458,12 +4454,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4473,12 +4469,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -4493,7 +4489,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4504,21 +4500,21 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Assist 3</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4534,12 +4530,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4549,12 +4545,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -4569,7 +4565,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4580,21 +4576,21 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 750 Coins / Consumable</t>
+          <t>Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4610,12 +4606,12 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4625,12 +4621,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4645,7 +4641,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4660,17 +4656,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3</t>
+          <t>The Final Challenge</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
+          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4686,12 +4682,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4701,12 +4697,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -4721,7 +4717,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -4732,21 +4728,21 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Finesse</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 500 Coins / Consumable</t>
+          <t>Evo Unlock / Consumable / 1,500 Coins</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -4762,12 +4758,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4777,12 +4773,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4797,7 +4793,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -4808,21 +4804,21 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Serial Winner</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
+          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4833,17 +4829,17 @@
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4853,12 +4849,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -4873,7 +4869,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4884,21 +4880,21 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective</t>
+          <t>PL Scorer</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective.</t>
+          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
+          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4909,17 +4905,17 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4929,12 +4925,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4949,7 +4945,7 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4960,21 +4956,21 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
+          <t>Assist 3</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Professional Challenge objective.</t>
+          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4985,17 +4981,17 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5005,12 +5001,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5025,7 +5021,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5036,21 +5032,21 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
+          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,500 Coins</t>
+          <t>Consumables Pack / 750 Coins / Consumable</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -5061,17 +5057,17 @@
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>G015</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5081,12 +5077,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5101,7 +5097,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5116,15 +5112,19 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Assist in 3</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
+          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -5138,12 +5138,12 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>4 Completions</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
+          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+          <t>Consumables Pack / 500 Coins / Consumable</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5260,21 +5260,21 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>3 Completions</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -5285,17 +5285,17 @@
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5336,21 +5336,21 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2 Completions</t>
+          <t>Complete the Ones We Watched World Class Challenge objective</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
+          <t>Complete the Ones We Watched World Class Challenge objective.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>4,000 Coins / 2,000 Coins</t>
+          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5361,17 +5361,17 @@
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -5412,21 +5412,21 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>1 Completion</t>
+          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
+          <t>Complete the Ones We Watched Professional Challenge objective.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>2,000 Coins</t>
+          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -5437,17 +5437,17 @@
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>G016</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched professional challenge objective.||complete the ones we watched professional challenge objectiv</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -5488,21 +5488,21 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Score in 9</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Complete the Ones We Watched Semi-Pro Challenge objective.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -5513,17 +5513,17 @@
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>G017</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched semi-pro challenge objective.||complete the ones we watched semi-pro challenge objective.</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -5568,20 +5568,20 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Win 1 match in any Football Ultimate Team game mode.</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
+          <t>Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -5590,30 +5590,42 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 25 days</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete all season 1: ones to watch exhibition weekly play objectives, to earn ones to watch ousmane diomandé, an evo and coins! all rewards are untradeable.||season 1: ones to watch exhibition completionist - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5628,20 +5640,24 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Barbecue Sauce</t>
+          <t>4 Completions</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
+          <t>13,000 Coins / 7,000 Coins / 4,000 Coins</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -5650,30 +5666,42 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 25 days</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from any premier league team and 1 player from any women's super league team in your starting 11.||barbecue sauce</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 4 times.||4 completions</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -5688,20 +5716,24 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Be a Goldfish</t>
+          <t>3 Completions</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
+          <t>7,000 Coins / 4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -5710,30 +5742,42 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 25 days</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 3 times.||3 completions</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -5748,20 +5792,24 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Unselfish Play</t>
+          <t>2 Completions</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
+          <t>4,000 Coins / 2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -5770,30 +5818,42 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr"/>
-      <c r="M52" s="3" t="inlineStr"/>
-      <c r="N52" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 25 days</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 2 times.||2 completions</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5808,20 +5868,24 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Football is Life</t>
+          <t>1 Completion</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in any Football Ultimate Team game mode.</t>
+          <t>Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr"/>
+          <t>2,000 Coins</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -5830,30 +5894,42 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>G018</t>
+          <t>G016</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="3" t="inlineStr"/>
-      <c r="N53" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 25 days</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
+          <t>https://www.fut.gg/objectives/seasonal/79-season-1-ones-to-watch-exhibition-completionist/||complete the season 1: ones to watch exhibition weekly play objective 1 time.||1 completion</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -5868,22 +5944,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Score in 9</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Squad Battles Matches on any difficulty.</t>
+          <t>Score in 9 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
+          <t>Watch / FC Pro</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr"/>
@@ -5894,30 +5970,42 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G017</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="3" t="inlineStr"/>
-      <c r="N54" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 25 days</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/80-season-1-ones-to-watch-exhibition-weekly-play/||score in 9 separate matches in the season 1: ones to watch exhibition.||score in 9</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -5928,28 +6016,24 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Squad Battles Matches on any difficulty.</t>
+          <t>Win 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -5958,12 +6042,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5973,7 +6057,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr"/>
@@ -5981,7 +6065,7 @@
       <c r="N55" s="3" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||win 1 match in any football ultimate team game mode.||believe</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -5992,28 +6076,24 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Barbecue Sauce</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles Matches on any difficulty.</t>
+          <t>Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
+          <t>Stadium Tifo / Stadium Background Tifo</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -6022,12 +6102,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>G019</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6037,7 +6117,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr"/>
@@ -6045,7 +6125,7 @@
       <c r="N56" s="3" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||score 5 goals in any football ultimate team game mode while having at least 1 player from any premier league team and 1 player from any women's super league team in your starting 11.||barbecue sauce</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -6056,21 +6136,21 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Be a Goldfish</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Draft matches.</t>
+          <t>Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr"/>
@@ -6082,12 +6162,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6097,7 +6177,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr"/>
@@ -6105,7 +6185,7 @@
       <c r="N57" s="3" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 3 matches in any football ultimate team game mode while having at least 2 players from usa in your starting 11.||be a goldfish</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -6116,21 +6196,21 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Unselfish Play</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Draft matches.</t>
+          <t>Assist 4 goals in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+          <t>Stadium Tifo / Stadium Background Tifo / Badge</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr"/>
@@ -6142,12 +6222,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6157,7 +6237,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr"/>
@@ -6165,7 +6245,7 @@
       <c r="N58" s="3" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||assist 4 goals in any football ultimate team game mode.||unselfish play</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -6176,21 +6256,21 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Football is Life</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Draft matches.</t>
+          <t>Play 1 match in any Football Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+          <t>Badge</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr"/>
@@ -6202,12 +6282,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>G020</t>
+          <t>G018</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6217,7 +6297,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr"/>
@@ -6225,7 +6305,7 @@
       <c r="N59" s="3" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/98-ted-lassos-masterclass/||play 1 match in any football ultimate team game mode.||football is life</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -6240,20 +6320,24 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Play 50</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Play 50 Co-Op matches.</t>
+          <t>Play 15 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr"/>
+          <t>2x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -6262,12 +6346,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -6277,7 +6361,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr"/>
@@ -6285,7 +6369,7 @@
       <c r="N60" s="3" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 15 squad battles matches on any difficulty.||play 15</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -6305,15 +6389,19 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Co-Op matches.</t>
+          <t>Play 10 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr"/>
+          <t>75+ Gold Player Pack / X2 Players Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -6322,12 +6410,12 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -6337,7 +6425,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr"/>
@@ -6345,7 +6433,7 @@
       <c r="N61" s="3" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 10 squad battles matches on any difficulty.||play 10</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -6365,15 +6453,19 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Co-Op matches.</t>
+          <t>Play 5 Squad Battles Matches on any difficulty.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
+          <t>75+ Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -6382,12 +6474,12 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>G021</t>
+          <t>G019</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Battles Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -6397,7 +6489,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr"/>
@@ -6405,7 +6497,7 @@
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/42-squad-battles-milestone/||play 5 squad battles matches on any difficulty.||play 5</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -6420,24 +6512,20 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Score 20</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Score 20 goals as a team in Rush.</t>
+          <t>Play 15 Draft matches.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x Large Gold Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -6446,12 +6534,12 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -6461,7 +6549,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr"/>
@@ -6469,7 +6557,7 @@
       <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 15 draft matches.||play 15</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
@@ -6484,24 +6572,20 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Bonuses</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Complete 20 Rush bonuses.</t>
+          <t>Play 10 Draft matches.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
@@ -6510,12 +6594,12 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -6525,7 +6609,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr"/>
@@ -6533,7 +6617,7 @@
       <c r="N64" s="3" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 10 draft matches.||play 10</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -6548,24 +6632,20 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Bonuses</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Rush bonuses.</t>
+          <t>Play 5 Draft matches.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -6574,12 +6654,12 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G020</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Draft Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -6589,7 +6669,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr"/>
@@ -6597,7 +6677,7 @@
       <c r="N65" s="3" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
+          <t>https://www.fut.gg/objectives/milestones/45-draft-milestone/||play 5 draft matches.||play 5</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -6608,28 +6688,24 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 50</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rush matches.</t>
+          <t>Play 50 Co-Op matches.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 75+ Gold Player Pack / 1x x2 Players Pack / 1x 80+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
@@ -6638,12 +6714,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -6653,7 +6729,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr"/>
@@ -6661,7 +6737,7 @@
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 50 co-op matches.||play 50</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -6672,7 +6748,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -6681,19 +6757,15 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rush matches.</t>
+          <t>Play 10 Co-Op matches.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>75+ Gold Player Pack / X2 Players Pack / 1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -6702,12 +6774,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -6717,7 +6789,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr"/>
@@ -6725,7 +6797,7 @@
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 10 co-op matches.||play 10</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -6736,7 +6808,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -6745,19 +6817,15 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush matches.</t>
+          <t>Play 5 Co-Op matches.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1 Of 2 78+ Gold Player Pick / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
@@ -6766,12 +6834,12 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>G022</t>
+          <t>G021</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Co-Op Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -6781,7 +6849,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr"/>
@@ -6789,7 +6857,7 @@
       <c r="N68" s="3" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/46-co-op-milestone/||play 5 co-op matches.||play 5</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
@@ -6804,34 +6872,38 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your foot</t>
+          <t>Score 20</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
+          <t>Score 20 goals as a team in Rush.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 5,000 Coins</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr"/>
+          <t>1x Small Gold Players Pack / 3x 75+ Gold Player Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -6841,7 +6913,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr"/>
@@ -6849,7 +6921,7 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||score 20 goals as a team in rush.||score 20</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -6864,34 +6936,38 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Complete 20 Bonuses</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 60 Stars.</t>
+          <t>Complete 20 Rush bonuses.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr"/>
+          <t>Small Gold Players Pack / 2x 75+ Gold Player Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -6901,7 +6977,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr"/>
@@ -6909,7 +6985,7 @@
       <c r="N70" s="3" t="inlineStr"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 20 rush bonuses.||complete 20 bonuses</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
@@ -6924,34 +7000,38 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Complete 10 Bonuses</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 30 Stars.</t>
+          <t>Complete 10 Rush bonuses.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr"/>
+          <t>2x 75+ Gold Player Pack / 75+ Gold Player Pack / Jumbo Gold Pack</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -6961,7 +7041,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr"/>
@@ -6969,7 +7049,7 @@
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||complete 10 rush bonuses.||complete 10 bonuses</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -6984,34 +7064,38 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Complete Moments challenges to earn 15 Stars.</t>
+          <t>Play 15 Rush matches.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr"/>
+          <t>75+ Gold Player Pack / Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>G023</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -7021,7 +7105,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -7029,7 +7113,7 @@
       <c r="N72" s="3" t="inlineStr"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 15 rush matches.||play 15</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
@@ -7040,38 +7124,42 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Build your way up to become a Squad Building Master!</t>
+          <t>Play 10 Rush matches.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Large Gold Pack</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr"/>
+          <t>Jumbo Gold Pack / 1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -7081,7 +7169,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr"/>
@@ -7089,7 +7177,7 @@
       <c r="N73" s="3" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 10 rush matches.||play 10</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -7100,38 +7188,42 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Complete 25 Squad Building Challenge groups.</t>
+          <t>Play 5 Rush matches.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr"/>
+          <t>1 Of 2 78+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G022</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Rush Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -7141,7 +7233,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -7149,7 +7241,7 @@
       <c r="N74" s="3" t="inlineStr"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/50-rush-milestone/||play 5 rush matches.||play 5</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -7160,21 +7252,21 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>Complete Moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Complete 10 Squad Building Challenge groups.</t>
+          <t>Complete Moments challenges and earn stars to show your football dominance!</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+          <t>Coin Boost / 5,000 Coins</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr"/>
@@ -7186,12 +7278,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -7201,7 +7293,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr"/>
@@ -7209,7 +7301,7 @@
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges and earn stars to show your football dominance!||complete moments challenges and earn stars to show your foot</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
@@ -7220,21 +7312,21 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Complete 5 Squad Building Challenge groups.</t>
+          <t>Complete Moments challenges to earn 60 Stars.</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+          <t>1x Small Gold Players Pack / 1x Large Silver Players Pack / 1x Large Bronze Players Pack / Small Gold Players Pack</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr"/>
@@ -7246,12 +7338,12 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>G024</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -7261,7 +7353,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -7269,7 +7361,7 @@
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 60 stars.||complete moments challenges to earn 60 stars.</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -7280,42 +7372,38 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Get acquainted with Live Events matches.</t>
+          <t>Complete Moments challenges to earn 30 Stars.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Small Gold Players Pack / Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -7325,7 +7413,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr"/>
@@ -7333,7 +7421,7 @@
       <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 30 stars.||complete moments challenges to earn 30 stars.</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -7344,42 +7432,38 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Play 20</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Play 20 Live Events matches.</t>
+          <t>Complete Moments challenges to earn 15 Stars.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Large Silver Players Pack / Large Bronze Players Pack</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G023</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Moments Stars Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -7389,7 +7473,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -7397,7 +7481,7 @@
       <c r="N78" s="3" t="inlineStr"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
+          <t>https://www.fut.gg/objectives/milestones/51-moments-stars-milestone/||complete moments challenges to earn 15 stars.||complete moments challenges to earn 15 stars.</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -7408,42 +7492,38 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Live Events matches.</t>
+          <t>Build your way up to become a Squad Building Master!</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Large Gold Pack</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -7453,7 +7533,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr"/>
@@ -7461,7 +7541,7 @@
       <c r="N79" s="3" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||build your way up to become a squad building master!||build your way up to become a squad building master!</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
@@ -7472,42 +7552,38 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Live Events matches.</t>
+          <t>Complete 25 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>1x Small Gold Players Pack / 1x Jumbo Gold Pack / 1x Large Gold Pack / Small Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>G026</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -7517,7 +7593,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -7525,7 +7601,7 @@
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 25 squad building challenge groups.||complete 25 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
@@ -7536,42 +7612,38 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Rivals matches.</t>
+          <t>Complete 10 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>Rivals</t>
-        </is>
-      </c>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr"/>
       <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>G027</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -7581,7 +7653,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr"/>
@@ -7589,7 +7661,7 @@
       <c r="N81" s="3" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 10 squad building challenge groups.||complete 10 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
@@ -7600,42 +7672,38 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Rivals matches.</t>
+          <t>Complete 5 Squad Building Challenge groups.</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>Rivals</t>
-        </is>
-      </c>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>G027</t>
+          <t>G024</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Squad Building Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -7645,7 +7713,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -7653,7 +7721,7 @@
       <c r="N82" s="3" t="inlineStr"/>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/49-squad-building-milestone/||complete 5 squad building challenge groups.||complete 5 squad building challenge groups.</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
@@ -7664,26 +7732,26 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals matches.</t>
+          <t>Get acquainted with Live Events matches.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
+          <t>1 Of 2 80+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr"/>
@@ -7694,12 +7762,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>G027</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -7709,7 +7777,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr"/>
@@ -7717,7 +7785,7 @@
       <c r="N83" s="3" t="inlineStr"/>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||get acquainted with live events matches.||live events milestone - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
@@ -7728,26 +7796,26 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 20</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Play 15 Champions matches.</t>
+          <t>Play 20 Live Events matches.</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
+          <t>1 Of 2 80+ Gold Player Pick / 1x Small Gold Players Pack / 1x Jumbo Gold Pack / Small Gold Players Pack</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr"/>
@@ -7758,12 +7826,12 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>G028</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -7773,7 +7841,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -7781,7 +7849,7 @@
       <c r="N84" s="3" t="inlineStr"/>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 20 live events matches.||play 20</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -7792,7 +7860,7 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
@@ -7801,17 +7869,17 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Play 10 Champions matches.</t>
+          <t>Play 10 Live Events matches.</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+          <t>Small Gold Players Pack / Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr"/>
@@ -7822,12 +7890,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>G028</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -7837,7 +7905,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr"/>
@@ -7845,7 +7913,7 @@
       <c r="N85" s="3" t="inlineStr"/>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 10 live events matches.||play 10</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
@@ -7856,7 +7924,7 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
@@ -7865,17 +7933,17 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions matches.</t>
+          <t>Play 5 Live Events matches.</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>75-83 Gold Player Pack / Coin Boost</t>
+          <t>Jumbo Gold Pack / 1 Of 3 79+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Champions</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr"/>
@@ -7886,12 +7954,12 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>G028</t>
+          <t>G026</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+          <t>Live Events Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
@@ -7901,7 +7969,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -7909,7 +7977,7 @@
       <c r="N86" s="3" t="inlineStr"/>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+          <t>https://www.fut.gg/objectives/milestones/48-live-events-milestone/||play 5 live events matches.||play 5</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
@@ -7924,20 +7992,24 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Score 10 goals in any FUT game mode using an English player.</t>
+          <t>Play 15 Rivals matches.</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>500 SP / 50 SP</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr"/>
+          <t>1 Of 2 77+ Gold Player Pick / 1x 75+ Gold Player Pack / 1x 2x 82+ Gold Players Pack / 75+ Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -7946,42 +8018,30 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>G030</t>
+          <t>G027</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N87" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
+      <c r="N87" s="3" t="inlineStr"/>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 15 rivals matches.||play 15</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
@@ -7996,29 +8056,25 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+          <t>Play 10 Rivals matches.</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+          <t>75+ Gold Player Pack / 5,000 Coins / 1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>Rivals</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -8026,42 +8082,30 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>G030</t>
+          <t>G027</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr"/>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 10 rivals matches.||play 10</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
@@ -8076,22 +8120,22 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
+          <t>Play 5 Rivals matches.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+          <t>1 Of 2 78+ Gold Player Pick / 1 Of 2 77+ Gold Player Pick</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Rush</t>
+          <t>Rivals</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr"/>
@@ -8102,42 +8146,30 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>G030</t>
+          <t>G027</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+          <t>Rivals Milestone - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>10/2 02:00</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="3" t="inlineStr"/>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
+          <t>https://www.fut.gg/objectives/milestones/43-rivals-milestone/||play 5 rivals matches.||play 5</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
@@ -8152,20 +8184,24 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Scoring Success</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals in any FUT game mode.</t>
+          <t>Play 15 Champions matches.</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>10 SP</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr"/>
+          <t>1x 4x 81+ Gold Players Pack / 1x 75-83 Gold Player Pack / 1x 81+ Gold Player Pack / 4X 81+ Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
       <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" s="3" t="inlineStr">
         <is>
@@ -8174,52 +8210,468 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
+          <t>G028</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 15 champions matches.||play 15</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>4X 81+ Gold Players Pack / 75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>G028</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 10 champions matches.||play 10</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Play 5 Champions matches.</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>75-83 Gold Player Pack / Coin Boost</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>G028</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>Champions Milestone - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr"/>
+      <c r="N92" s="3" t="inlineStr"/>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/milestones/44-champions-milestone/||play 5 champions matches.||play 5</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Score 10</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Score 10 goals in any FUT game mode using an English player.</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>500 SP / 50 SP</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr"/>
+      <c r="F93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||score 10 goals in any fut game mode using an english player.||score 10</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Win 10</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush).</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rivals/champions/live events/rush).||win 10</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Play 10</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals).</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>50 SP / Buy 10 Player Items using Buy Now in the Transfer Market. / List 10 player items in the Transfer Market.</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Rush</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>Weekly Objectives - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>10/2 02:00</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:00+09:00</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/objectives/seasonal/65-weekly-objectives/||play 10 matches in squad battles on any difficulty (or rush/rivals).||play 10</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Scoring Success</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Score 2 goals in any FUT game mode.</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>10 SP</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>description_line_with_backward_title</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
           <t>G031</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>Daily Objectives - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="K90" s="3" t="inlineStr">
+      <c r="K96" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/</t>
         </is>
       </c>
-      <c r="L90" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 6 days</t>
-        </is>
-      </c>
-      <c r="M90" s="3" t="inlineStr">
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 5 days</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
         <is>
           <t>10/2 02:00</t>
         </is>
       </c>
-      <c r="N90" s="3" t="inlineStr">
+      <c r="N96" s="3" t="inlineStr">
         <is>
           <t>2026-10-02T02:00+09:00</t>
         </is>
       </c>
-      <c r="O90" s="3" t="inlineStr">
+      <c r="O96" s="3" t="inlineStr">
         <is>
           <t>https://www.fut.gg/objectives/seasonal/61-daily-objectives/||score 2 goals in any fut game mode.||scoring success</t>
         </is>
       </c>
-      <c r="P90" s="3" t="inlineStr">
+      <c r="P96" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P90"/>
+  <autoFilter ref="A1:P96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8292,12 +8744,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP</t>
+          <t>NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. Shunsuke Mito 100 SP</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP Expires in 7 days 200 total 5 Objectives 92% 8%</t>
+          <t>NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. Shunsuke Mito 100 SP Expires in 7 days 200 total 5 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -8307,12 +8759,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>10/3 02:00</t>
+          <t>10/4 02:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03T02:00+09:00</t>
+          <t>2026-10-04T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -8329,17 +8781,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock</t>
+          <t>NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock Expires in 7 days 300 total 6 Objectives 78% 22%</t>
+          <t>NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Expires in 6 days 300 total 6 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -8371,7 +8823,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 94% 6%</t>
+          <t>NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -8396,12 +8848,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 4 days 5 Objectives 91% 9%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 3 days 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8433,22 +8885,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 1 day 3 Objectives 64% 36%</t>
+          <t>Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 11 hours 3 Objectives 64% 36%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9/27 02:00</t>
+          <t>9/27 13:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T02:00+09:00</t>
+          <t>2026-09-27T13:00+09:00</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8922,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 9 days 2 Objectives 10% 90%</t>
+          <t>FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 8 days 2 Objectives 10% 90%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -8532,12 +8984,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 4 days 2 Objectives 56% 44%</t>
+          <t>FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 3 days 2 Objectives 57% 43%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -8569,12 +9021,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 26 days 7 Objectives 87% 13%</t>
+          <t>Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 25 days 7 Objectives 87% 13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8606,12 +9058,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 26 days 4 Objectives 81% 19%</t>
+          <t>Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 25 days 4 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8643,12 +9095,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 26 days 4 Objectives 90% 10%</t>
+          <t>Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 25 days 4 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -8680,12 +9132,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 26 days 4 Objectives 86% 14%</t>
+          <t>Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 25 days 4 Objectives 88% 13%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8717,12 +9169,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 26 days 4 Objectives 91% 9%</t>
+          <t>Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 25 days 4 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8754,12 +9206,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 26 days 4 Objectives 93% 7%</t>
+          <t>Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 25 days 4 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8791,12 +9243,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 26 days 4 Objectives 91% 9%</t>
+          <t>Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 25 days 4 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8828,12 +9280,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 26 days 4 Objectives 90% 10%</t>
+          <t>Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 25 days 4 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8865,12 +9317,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 26 days 1 Objectives 85% 15%</t>
+          <t>Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 25 days 1 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -8902,7 +9354,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 95% 5%</t>
+          <t>Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -8927,7 +9379,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 91% 9%</t>
+          <t>Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -8952,7 +9404,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8%</t>
+          <t>Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -8977,7 +9429,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 81% 19%</t>
+          <t>Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -9002,7 +9454,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 90% 10%</t>
+          <t>Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -9027,7 +9479,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 85% 15%</t>
+          <t>Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -9052,7 +9504,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9%</t>
+          <t>Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -9177,7 +9629,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 79% 21%</t>
+          <t>Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 76% 24%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -9202,12 +9654,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 6 days 500 total 5 Objectives 93% 7%</t>
+          <t>Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 5 days 500 total 5 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -9239,12 +9691,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 6 days 30 total 2 Objectives 93% 7%</t>
+          <t>Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 5 days 30 total 2 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -9319,7 +9771,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. 100 SP Expires in 7 days 200 total 5 Objectives 92% 8% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. Shunsuke Mito 100 SP Expires in 7 days 200 total 5 Objectives 92% 8% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9793,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Evo Unlock Expires in 7 days 300 total 6 Objectives 78% 22% Rewards 300 SP 5,000 Coins Award Evo Unlock 1 Of 3 Destined For Glory W1 Loan Pick Evo Unlock 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. Evo Unlock 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Expires in 6 days 300 total 6 Objectives 79% 21% Rewards 300 SP 5,000 Coins Award 1 Of 3 Destined For Glory W1 Loan Pick 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9815,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 94% 6% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 90% 10% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9837,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 4 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 3 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9859,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 1 day 3 Objectives 64% 36% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 11 hours 3 Objectives 64% 36% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9881,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 9 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 8 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9473,73 +9925,73 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 4 days 2 Objectives 56% 44% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 3 days 2 Objectives 57% 43% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 26 days 4 Objectives 81% 19% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 25 days 7 Objectives 87% 13% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 26 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 25 days 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>G012</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 26 days 4 Objectives 86% 14% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 25 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9561,7 +10013,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 26 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 25 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9583,7 +10035,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 26 days 4 Objectives 93% 7% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 25 days 4 Objectives 94% 6% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9605,7 +10057,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 26 days 4 Objectives 91% 9% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 25 days 4 Objectives 92% 8% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9627,7 +10079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 26 days 4 Objectives 90% 10% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 25 days 4 Objectives 89% 11% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9649,7 +10101,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 26 days 1 Objectives 85% 15% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 25 days 1 Objectives 86% 14% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9671,7 +10123,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 95% 5% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9693,7 +10145,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 91% 9% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Milestone Squad Battles Milestone - EA SPORTS FC 27 Objectives The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Squad Battles Milestone The challenge is set. Take to the pitch in Squad Battles and battle through the competition. Large Gold Pack 3 Objectives 92% 8% Rewards Coin Boost 2x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Squad Battles Matches on any difficulty. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Squad Battles Matches on any difficulty. 75+ Gold Player Pack Play 5 Play 5 Squad Battles Matches on any difficulty. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9715,7 +10167,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Draft Milestone Draft Milestone - EA SPORTS FC 27 Objectives Draft your path to greatness! Draft Milestone Draft your path to greatness! Large Gold Pack 3 Objectives 93% 7% Rewards 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x Large Gold Pack Play 15 Play 15 Draft matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Draft matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Draft matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9737,7 +10189,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 81% 19% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 82% 18% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9759,7 +10211,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 90% 10% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rush Milestone Rush Milestone - EA SPORTS FC 27 Objectives Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! Rush Milestone Squad up and complete Rush bonuses alongside other players as you try to reign supreme in Rush! 1 Of 2 78+ Gold Player Pick Coin Boost 6 Objectives 91% 9% Rewards 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick 1 Of 2 78+ Gold Player Pick Coin Boost 1x Small Gold Players Pack 3x 75+ Gold Player Pack 1x Jumbo Gold Pack Score 20 Score 20 goals as a team in Rush. Small Gold Players Pack Complete 20 Bonuses Complete 20 Rush bonuses. 2x 75+ Gold Player Pack Complete 10 Bonuses Complete 10 Rush bonuses. 75+ Gold Player Pack Play 15 Play 15 Rush matches. Jumbo Gold Pack Play 10 Play 10 Rush matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rush matches. 1 Of 2 78+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9781,7 +10233,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 85% 15% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 86% 14% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9803,7 +10255,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 91% 9% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9913,7 +10365,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 79% 21% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 76% 24% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9935,7 +10387,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 6 days 500 total 5 Objectives 93% 7% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 5 days 500 total 5 Objectives 93% 7% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9957,7 +10409,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 6 days 30 total 2 Objectives 93% 7% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 5 days 30 total 2 Objectives 93% 7% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -9995,14 +10447,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TimeoutError: Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/", waiting until "networkidle"
+  - navigating to "https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manifest'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mission_Groups'!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objective_Raw'!$A$1:$P$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Collected_URLs'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Page_Text'!$A$1:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Errors'!$A$1:$B$4</definedName>
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 04:34:28</t>
+          <t>2026-09-28 05:00:20</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 02:00:00</t>
+          <t>2026-09-28 02:00:00</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -646,7 +646,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. NEW Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. Shunsuke Mito 100 SP Expires in 7 days 200 total 5 Objectives 92% 8% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaigns &gt; Squad Foundations: Shunsuke Mito Squad Foundations: Shunsuke Mito - EA SPORTS FC 27 Objectives Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. Squad Foundations: Shunsuke Mito Complete these objectives to earn Squad Foundations Shunsuke Mito and SP! All rewards are untradeable. Shunsuke Mito 100 SP Expires in 6 days 200 total 5 Objectives 93% 7% Rewards 200 SP Award 1x 4x 83+ Gold Players Pack 1x 4x 82+ Gold Players Pack 1x 4x 81+ Gold Players Pack 1x 4x 80+ Gold Players Pack Winners Circle Win 7 matches in any FUT game mode. 4X 83+ Gold Players Pack Wide Threat Score at least 1 goal in 3 separate matches using a player with a Preferred Position of LM. 4X 82+ Gold Players Pack 100 SP EVO Ascension Complete any Evolution to earn an additional repeat of the Repeat Delivery Evolution. Award Smooth Samurai Score at least 1 goal in 4 separate matches using a Japanese player in any FUT game mode. 4X 81+ Gold Players Pack Composed Victory Win 3 matches in any FUT game mode while having min. 2 players from Eredivisie in your starting 11. 4X 80+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. NEW Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Expires in 6 days 300 total 6 Objectives 79% 21% Rewards 300 SP 5,000 Coins Award 1 Of 3 Destined For Glory W1 Loan Pick 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Destined for Glory Exhibition Destined for Glory Exhibition - EA SPORTS FC 27 Objectives Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Destined for Glory Exhibition Compete in the Destined for Glory Exhibition Live Event to earn multiple types of rewards and Squad Foundations Edouard Michut. All rewards are untradeable. Édouard Michut Expires in 5 days 300 total 6 Objectives 78% 22% Rewards 300 SP 5,000 Coins Award 1 Of 3 Destined For Glory W1 Loan Pick 1x 5x 78+ Gold Players Pack 1x 10x 75+ Gold Players Pack Score 1 Score 1 goal from outside the box in the Destined for Glory Exhibition Live Event. 5,000 Coins 200 SP Score in 7 Score at least 1 goal in 7 separate matches in the Destined for Glory Exhibition Live Event. 5X 78+ Gold Players Pack Score 5 Score 5 Low Driven goals in the Destined for Glory Exhibition Live Event. Award Win 3 Win 3 matches in the Destined for Glory Exhibition Live Event while having min. 2 French players in your starting 11. 10X 75+ Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Destined for Glory Exhibition Live Event while having min. 1 Destined for Glory player in your starting 11. 100 SP Play 1 Play 1 match in the Destined for Glory Exhibition Live Event. 1 Of 3 Destined For Glory W1 Loan Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. NEW Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 90% 10% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Foundations Gallery Foundations - EA SPORTS FC 27 Objectives Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. Gallery Foundations Learn the basics of the Gallery! Grade and complete Sets, achieve Rank S, and increase your Gallery Level as you explore everything the Gallery has to offer. All rewards are untradeable. 1,000 Coins 5 Gallery Tokens 5 Objectives 90% 10% Rewards 5 Gallery Tokens 1,250 Coins 1x 75+ Gold Player Pack 1x Jumbo Gold Pack 1x Small Silver Players Pack 1x Jumbo Bronze Pack Level Up Earn Gallery Score and reach Gallery Level 2. 75+ Gold Player Pack Three of a Kind Complete 3 Sets in the Gallery. Jumbo Gold Pack Set the Standard Achieve Rank S on any Set in the Gallery. Small Silver Players Pack Set in Motion Complete the Starter Set and get familiar with the Gallery. Jumbo Bronze Pack Make the Grade Grade any Set in the Gallery and see how your squad measures up. 250 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 3 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 27 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points and pack rewards! All rewards are untradeable. 2X 84+ Gold Players Pack Expires in 2 days 5 Objectives 91% 9% Rewards 1x 83+ Gold Player Pack 1x 2x 82+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x 2x 84+ Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 83+ Gold Player Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 2X 82+ Gold Players Pack 20,000 Rush Points Earn 20,000 points by completing bonuses in Rush. 2X 80+ Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 2X 78+ Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -834,42 +834,42 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 11 hours</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>9/27 13:00</t>
+          <t>10/5 02:00</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T13:00+09:00</t>
+          <t>2026-10-05T02:00+09:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Squad Battles: Champions Qualification Points Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives Compete in Squad Battles to earn Champions Qualification Points! Squad Battles: Champions Qualification Points Compete in Squad Battles to earn Champions Qualification Points! 100 Points Expires in 11 hours 3 Objectives 64% 36% Rewards 100 Points 100 Points 50 Points 100 Points Win 15 Win 15 matches in Squad Battles on min. World Class difficulty. 100 Points Win 12 Win 12 matches in Squad Battles on min. World Class difficulty. 100 Points Win 10 Win 10 matches in Squad Battles on min. World Class difficulty. 50 Points © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 7 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -878,48 +878,36 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>10/5 02:00</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Open Ladder FC Pro Open Ladder - EA SPORTS FC 27 Objectives Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. FC Pro Open Ladder Show your skills in the FC Pro Open Ladder to complete the group and earn rewards. All rewards are untradeable. Badge Expires in 8 days 2 Objectives 10% 90% Rewards Badge Adidas Cnxt25 Pro Ball Badge Compete Play 5 matches in the FC Pro Open Ladder. Badge Reach Division 5 Rivals Reach Division 5 in Rivals to qualify for the FC Pro Open Ladder. Adidas Cnxt25 Pro Ball © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 96% 4% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -928,36 +916,48 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Claim the Armband Claim the Armband - EA SPORTS FC 27 Objectives Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. Claim the Armband Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. 1 Of 4 Squad Foundations Pick 1 Objectives 96% 4% Rewards 500 Coins 1 Of 4 Squad Foundations Pick Play 1 Play a match in any FUT game mode. 500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 2 days 2 Objectives 56% 44% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -966,48 +966,48 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>10/22 02:00</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-10-22T02:00+09:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC 27 First Gameplay FC 27 First Gameplay - EA SPORTS FC 27 Objectives Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. FC 27 First Gameplay Join in on the action of the FC 27 First Gameplay broadcast on Twitch/EASPORTSFC or YouTube/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. Small Gold Players Pack Expires in 3 days 2 Objectives 57% 43% Rewards 2,500 Coins Coin Boost 1x Small Electrum Players Pack 1x Small Gold Players Pack Hit the Pitch Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Coin Boost 2,500 Coins Kick Off Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC. Small Electrum Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 24 days 7 Objectives 86% 14% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1016,18 +1016,18 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Season 1: Ones to Watch Exhibition Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable. Crysencio Summerville Expires in 25 days 7 Objectives 87% 13% Rewards Consumable 1x 2x 81+ Gold Players Pack 1x 2x 80+ Gold Players Pack 1x 80+ Gold Player Pack 1x 2x 78+ Gold Players Pack 1x 2x 75+ Gold Players Pack 1x Consumables Pack Score in 30 Score in 30 separate matches in the Season 1: Ones to Watch Exhibition. 2X 81+ Gold Players Pack Score in 20 Score in 20 separate matches in the Season 1: Ones to Watch Exhibition. 2X 80+ Gold Players Pack Assist 20 Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition. 80+ Gold Player Pack Assist 15 Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition. 2X 78+ Gold Players Pack Play 15 Play 15 matches in the Season 1: Ones to Watch Exhibition. 2X 75+ Gold Players Pack Play 5 Play 5 matches in the Season 1: Ones to Watch Exhibition. Consumables Pack Play 1 Play 1 match in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 24 days 4 Objectives 84% 16% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Legendary Challenge Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. Ones We Watched Legendary Challenge Beat the Ones We Watched Legendary challenges to earn rewards. All rewards are untradeable. 15X 75+ Laliga Gold Players Pack Expires in 25 days 4 Objectives 83% 17% Rewards 5,000 Coins 1x 10x 75+ Gold Players Pack 1x 3x 80+ Gold Players Pack 1x 2x 78+ Gold Players Pack 1x 15x 75+ LALIGA Gold Players Pack The Final Challenge Win 4 matches in the Ones We Watched Legendary Challenge. 10X 75+ Gold Players Pack Defensive Masterclass Win 1 match in the Ones We Watched Legendary Challenge. 3X 80+ Gold Players Pack Score 5 Score 5 times in the Ones We Watched Legendary Challenge. 5,000 Coins Play 1 Play 1 match in the Ones We Watched Legendary Challenge. 2X 78+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 24 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1116,18 +1116,18 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched World Class Challenge Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. Ones We Watched World Class Challenge Beat the Ones We Watched World Class challenges to earn rewards. All rewards are untradeable. 5X 78+ Premier League Gold Players Pack Expires in 25 days 4 Objectives 90% 10% Rewards 1,500 Coins Evo Unlock Consumable 1x 2x 75+ Gold Players Pack 1x 5x 78+ Premier League Gold Players Pack Pep's Domination Win 1 match in the Ones We Watched World Class Challenge. Evo Unlock Finesse Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge. Consumable Serial Winner Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge. 1,500 Coins PL Scorer Score with a Premier League player in the Ones We Watched World Class Challenge. 2X 75+ Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Professional Challenge Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. Ones We Watched Professional Challenge Beat the Ones We Watched Professional Challenges to earn rewards. All rewards are untradeable. 3X 78+ Serie A Gold Players Pack Expires in 24 days 4 Objectives 89% 11% Rewards 1,750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 3x 78+ Serie A Gold Players Pack Top Scorer Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge. 2X 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Professional Challenge. 1,750 Coins Assister Assist 2 goals in 1 match in the Ones We Watched Professional Challenge. Consumables Pack Play 1 Play 1 match in the Ones We Watched Professional Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 25 days 4 Objectives 91% 9% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Semi-Pro Challenge Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. Ones We Watched Semi-Pro Challenge Beat the Ones We Watched Semi-Pro Challenges to earn rewards. All rewards are untradeable. 82+ Premier League Gold Player Pack Expires in 24 days 4 Objectives 90% 10% Rewards 750 Coins Consumable Consumable 1x 2x 75+ Gold Players Pack 1x Consumables Pack 1x 82+ Premier League Gold Player Pack Win 1 Win 1 match in the Ones We Watched Semi-Pro Challenge. 2X 75+ Gold Players Pack Assist 3 Assist 3 goals in the Ones We Watched Semi-Pro Challenge. Consumables Pack Play 2 Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge. 750 Coins Score 1 Score in the Ones We Watched Semi-Pro Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 25 days 4 Objectives 94% 6% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Kick Off Challenge Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. Ones We Watched Kick Off Challenge Beat the Ones We Watched Kick Off Challenges to earn rewards. All rewards are untradeable. 2X 75+ Gold Players Pack Expires in 24 days 4 Objectives 93% 7% Rewards 500 Coins Consumable Consumable 1x 80+ Gold Player Pack 1x Consumables Pack 1x 2x 75+ Gold Players Pack Win 1 Win 1 match in the Ones We Watched Kick Off Challenge. 80+ Gold Player Pack Assist in 3 Assist in 3 separate matches in the Ones We Watched Kick Off Challenge. Consumables Pack Play 2 Play 2 matches in the Ones We Watched Kick Off Challenge. 500 Coins Score 1 Score in the Ones We Watched Kick Off Challenge. Consumable Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 25 days 4 Objectives 92% 8% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Ones We Watched Challenge Completionist Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Ones We Watched Challenge Completionist Beat the Ones We Watched Objectives to earn rewards. All rewards are untradeable. Savinho Expires in 24 days 4 Objectives 90% 10% Rewards 16,000 Coins Ones We Watched Legendary Challenge Complete the Ones We Watched Legendary Challenge objective. 5,000 Coins Ones We Watched World Class Challenge Complete the Ones We Watched World Class Challenge objective. 4,500 Coins Ones We Watched Professional Challenge Complete the Ones We Watched Professional Challenge objective. 4,000 Coins Ones We Watched Semi-Pro Challenge Complete the Ones We Watched Semi-Pro Challenge objective. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 25 days 4 Objectives 89% 11% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Completionist Season 1: Ones to Watch Exhibition Completionist - EA SPORTS FC 27 Objectives Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Season 1: Ones to Watch Exhibition Completionist Complete all Season 1: Ones to Watch Exhibition Weekly Play Objectives, to earn Ones to Watch Ousmane Diomandé, an EVO and Coins! All rewards are untradeable. Ousmane Diomande Expires in 24 days 4 Objectives 88% 12% Rewards 13,000 Coins Award 4 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 4 times. 7,000 Coins 3 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 3 times. 4,000 Coins 2 Completions Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 2 times. 2,000 Coins 1 Completion Complete the Season 1: Ones to Watch Exhibition Weekly Play Objective 1 time. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 25 days 1 Objectives 86% 14% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 1: Ones to Watch Exhibition Weekly Play Season 1: Ones to Watch Exhibition Weekly Play - EA SPORTS FC 27 Objectives Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Season 1: Ones to Watch Exhibition Weekly Play Compete in the Season 1: Ones to Watch Exhibition to earn exclusive rewards! All rewards are untradeable. Consumable Expires in 24 days 1 Objectives 85% 15% Rewards Consumable Consumable Score in 9 Score in 9 separate matches in the Season 1: Ones to Watch Exhibition. Consumable © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 94% 6% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Ted Lasso's Masterclass Ted Lasso's Masterclass - EA SPORTS FC 27 Objectives Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Ted Lasso's Masterclass Complete challenges celebrating manager Ted Lasso and AFC Richmond to earn exclusive rewards! All rewards are untradeable. Manager Evo Unlock 6 Objectives 93% 7% Rewards Award Manager Award Stadium Tifo Stadium Background Tifo Badge Stadium Stadium Theme Award Manager Evo Unlock Believe Win 1 match in any Football Ultimate Team game mode. Award Biscuits with the Boss Build 20+ Chemistry in your squad. Manager Barbecue Sauce Score 5 goals in any Football Ultimate Team game mode while having at least 1 player from any Premier League team and 1 player from any Women's Super League team in your starting 11. Award Be a Goldfish Play 3 matches in any Football Ultimate Team game mode while having at least 2 players from USA in your starting 11. Stadium Tifo Stadium Background Tifo Unselfish Play Assist 4 goals in any Football Ultimate Team game mode. Badge Stadium Stadium Theme Football is Life Play 1 match in any Football Ultimate Team game mode. Award © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1559,7 +1559,7 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 82% 18% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Co-Op Milestone Co-Op Milestone - EA SPORTS FC 27 Objectives Team up with Friends to embark on the Co-op journey! Co-Op Milestone Team up with Friends to embark on the Co-op journey! 80+ Gold Player Pack 5,000 Coins 3 Objectives 79% 21% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick Coin Boost 1x 75+ Gold Player Pack 1x x2 Players Pack 1x 80+ Gold Player Pack Play 50 Play 50 Co-Op matches. 75+ Gold Player Pack X2 Players Pack Play 10 Play 10 Co-Op matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Co-Op matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1635,7 +1635,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 86% 14% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Moments Stars Milestone Moments Stars Milestone - EA SPORTS FC 27 Objectives Complete Moments challenges and earn stars to show your football dominance! Moments Stars Milestone Complete Moments challenges and earn stars to show your football dominance! Coin Boost 5,000 Coins 3 Objectives 87% 13% Rewards 5,000 Coins Coin Boost 1x Small Gold Players Pack 1x Large Silver Players Pack 1x Large Bronze Players Pack 60 Stars Complete Moments challenges to earn 60 Stars. Small Gold Players Pack 30 Stars Complete Moments challenges to earn 30 Stars. Large Silver Players Pack 15 Stars Complete Moments challenges to earn 15 Stars. Large Bronze Players Pack © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1673,7 +1673,7 @@
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 92% 8% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Building Milestone Squad Building Milestone - EA SPORTS FC 27 Objectives Build your way up to become a Squad Building Master! Squad Building Milestone Build your way up to become a Squad Building Master! Large Gold Pack 3 Objectives 89% 11% Rewards 1 Of 3 79+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack 1x Large Gold Pack 25 SBCs Complete 25 Squad Building Challenge groups. Small Gold Players Pack 10 SBCs Complete 10 Squad Building Challenge groups. Jumbo Gold Pack 5 SBCs Complete 5 Squad Building Challenge groups. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 93% 7% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Transfer Market Milestone Transfer Market Milestone - EA SPORTS FC 27 Objectives Wheel and deal your way to Transfer Market Mastery! Transfer Market Milestone Wheel and deal your way to Transfer Market Mastery! Coin Boost 4 Objectives 88% 13% Rewards 15,000 Coins Coin Boost List 50 List 50 players on the Transfer Market. 5,000 Coins List 25 List 25 players on the Transfer Market. 2,500 Coins 50 Buy Now Buy 50 players using Buy Now on the Transfer Market. 5,000 Coins 25 Buy Now Buy 25 players using Buy Now on the Transfer Market. 2,500 Coins © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1749,7 +1749,7 @@
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 92% 8% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Milestone Live Events Milestone - EA SPORTS FC 27 Objectives Get acquainted with Live Events matches. Live Events Milestone Get acquainted with Live Events matches. 1 Of 2 80+ Gold Player Pick 3 Objectives 90% 10% Rewards 1 Of 3 79+ Gold Player Pick 1 Of 2 80+ Gold Player Pick 1x Small Gold Players Pack 1x Jumbo Gold Pack Play 20 Play 20 Live Events matches. Small Gold Players Pack Play 10 Play 10 Live Events matches. Jumbo Gold Pack Play 5 Play 5 Live Events matches. 1 Of 3 79+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 91% 9% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Milestone Rivals Milestone - EA SPORTS FC 27 Objectives The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. Rivals Milestone The ultimate test of skill awaits in Division Rivals. Battle against the competition and emerge victorious. 2X 82+ Gold Players Pack 3 Objectives 85% 15% Rewards 5,000 Coins 1 Of 2 78+ Gold Player Pick 1 Of 2 77+ Gold Player Pick 1x 75+ Gold Player Pack 1x 2x 82+ Gold Players Pack Play 15 Play 15 Rivals matches. 75+ Gold Player Pack 5,000 Coins Play 10 Play 10 Rivals matches. 1 Of 2 78+ Gold Player Pick Play 5 Play 5 Rivals matches. 1 Of 2 77+ Gold Player Pick © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 89% 11% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Champions Milestone Champions Milestone - EA SPORTS FC 27 Objectives Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. Champions Milestone Every legend has a beginning. Enter Champions and begin your path to becoming the Golden G.O.A.T. 81+ Gold Player Pack 5,000 Coins 3 Objectives 77% 23% Rewards 5,000 Coins Coin Boost 1x 4x 81+ Gold Players Pack 1x 75-83 Gold Player Pack 1x 81+ Gold Player Pack Play 15 Play 15 Champions matches. 4X 81+ Gold Players Pack Play 10 Play 10 Champions matches. 75-83 Gold Player Pack Play 5 Play 5 Champions matches. Coin Boost © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1863,7 +1863,7 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 76% 24% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Gallery Milestone Gallery Milestone - EA SPORTS FC 27 Objectives Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Gallery Milestone Grow your Gallery Score, hit new levels, and earn rewards to build the ultimate club showcase! Evo Unlock 5 Objectives 72% 28% Rewards 1 Of 5 92+ Holographic Base Icon Player Pick 1 Of 5 88+ Holographic Base Hero Player Pick 1 Of 5 Holographic Base Icon Player Pick 1 Of 5 Holographic Base Hero Player Pick Evo Unlock Level 25 Reach Gallery Level 25. 1 Of 5 92+ Holographic Base Icon Player Pick Level 20 Reach Gallery Level 20. 1 Of 5 88+ Holographic Base Hero Player Pick Level 15 Reach Gallery Level 15. 1 Of 5 Holographic Base Icon Player Pick Level 10 Reach Gallery Level 10. 1 Of 5 Holographic Base Hero Player Pick Level 5 Reach Gallery Level 5. Jesús Corona © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 5 days 500 total 5 Objectives 93% 7% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 27 Objectives Complete Weekly Objectives to earn SP! Weekly Objectives Complete Weekly Objectives to earn SP! 250 SP Expires in 4 days 500 total 5 Objectives 86% 14% Rewards 500 SP Score 10 Score 10 goals in any FUT game mode using an English player. 50 SP Win 10 Win 10 matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush). 50 SP Play 10 Play 10 matches in Squad Battles on any difficulty (or Rush/Rivals). 50 SP Buy 10 Buy 10 Player Items using Buy Now in the Transfer Market. 50 SP List 10 List 10 player items in the Transfer Market. 50 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 5 days 30 total 2 Objectives 93% 7% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 27 Objectives Play, complete and earn SP from daily objective every 24 hours! Daily Objectives Play, complete and earn SP from daily objective every 24 hours! 10 SP Expires in 4 days 30 total 2 Objectives 91% 9% Rewards 30 SP Play 1 Play 1 match in any FUT game mode. 10 SP Scoring Success Score 2 goals in any FUT game mode. 10 SP © 2026 Stormstrike Inc. All rights reserved. Your Privacy Choices About | Editorial Policy | Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -3356,25 +3356,25 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Win 15</t>
+          <t>Compete</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Win 15 matches in Squad Battles on min. World Class difficulty.</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
+          <t>Play 5 matches in the FC Pro Open Ladder.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Badge</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Min. World Class</t>
-        </is>
-      </c>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3382,42 +3382,42 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 11 hours</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>9/27 13:00</t>
+          <t>10/5 02:00</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27T13:00+09:00</t>
+          <t>2026-10-05T02:00+09:00</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 15 matches in squad battles on min. world class difficulty.||win 15</t>
+          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/||play 5 matches in the fc pro open ladder.||compete</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3428,42 +3428,38 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Win 12</t>
+          <t>Claim the Armband</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Win 12 matches in Squad Battles on min. World Class difficulty.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Min. World Class</t>
-        </is>
-      </c>
+          <t>Claim the Armband</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -3473,27 +3469,15 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 11 hours</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>9/27 13:00</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27T13:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 12 matches in squad battles on min. world class difficulty.||win 12</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband||claim the armband</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3504,42 +3488,38 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on min. World Class difficulty.</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Min. World Class</t>
-        </is>
-      </c>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles: Champions Qualification Points - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3549,27 +3529,15 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 11 hours</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>9/27 13:00</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27T13:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/93-squad-battles-champions-qualification-points/||win 10 matches in squad battles on min. world class difficulty.||win 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband - ea sports fc 27 objectives||claim the armband - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -3580,72 +3548,56 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Compete</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in the FC Pro Open Ladder.</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Watch / FC Pro</t>
-        </is>
-      </c>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>FC Pro Open Ladder - EA SPORTS FC 27 Objectives</t>
+          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 8 days</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>10/5 02:00</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/108-fc-pro-open-ladder/||play 5 matches in the fc pro open ladder.||compete</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play 1||play 1</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3656,21 +3608,21 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband</t>
+          <t>Play a match in any FUT game mode.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
+          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
@@ -3705,7 +3657,7 @@
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband||claim the armband</t>
+          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play a match in any fut game mode.||play a match in any fut game mode.</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3716,56 +3668,72 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Hit the Pitch</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Complete this objective and choose 1 Squad Foundations Player Item from: Miley (Premier League), Moi Gómez (LALIGA EA SPORTS), Banzuzi (Bundesliga), or Danois (Ligue 1). All rewards are untradeable. / 1 Of 4 Squad Foundations Pick</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
+          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||claim the armband - ea sports fc 27 objectives||claim the armband - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3776,56 +3744,72 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Kick Off</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
+          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>FC Pro</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 days</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>9/30 02:00</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play 1||play 1</t>
+          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3836,38 +3820,38 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Play a match in any FUT game mode.</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Play a match in any FUT game mode.</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>500 Coins / 1 Of 4 Squad Foundations Pick</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
+          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Watch / FC Pro</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Claim the Armband - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3877,15 +3861,27 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 24 days</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>10/22 02:00</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/112-claim-the-armband/||play a match in any fut game mode.||play a match in any fut game mode.</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3896,21 +3892,21 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Hit the Pitch</t>
+          <t>Score in 30</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 60 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 1x Small Electrum Players Pack / 1x Small Gold Players Pack / 2,500 Coins</t>
+          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3926,42 +3922,42 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>10/22 02:00</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-10-22T02:00+09:00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 60 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||hit the pitch</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3972,21 +3968,21 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Kick Off</t>
+          <t>Score in 20</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Watch the FC 27 First Gameplay broadcast for at least 15 minutes. Broadcast will go live on September 15th at 17:00 UTC until 18:30 UTC.</t>
+          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Coin Boost / 2,500 Coins / Small Electrum Players Pack</t>
+          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4002,42 +3998,42 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>FC 27 First Gameplay - EA SPORTS FC 27 Objectives</t>
+          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>FC Pro</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>9/30 02:00</t>
+          <t>10/22 02:00</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30T02:00+09:00</t>
+          <t>2026-10-22T02:00+09:00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/fc-pro/90-fc-27-first-gameplay/||watch the fc 27 first gameplay broadcast for at least 15 minutes. broadcast will go live on september 15th at 17:00 utc until 18:30 utc.||kick off</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -4048,19 +4044,23 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Assist 20</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Complete the below challenges in the Season 1: Ones to Watch Exhibition. All rewards are untradeable.</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
+          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Watch / FC Pro</t>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||complete the below challenges in the season 1: ones to watch exhibition. all rewards are untradeable.||season 1: ones to watch exhibition - ea sports fc 27 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4120,21 +4120,21 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Score in 30</t>
+          <t>Assist 15</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Score in 30 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 78+ Gold Players Pack / 1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 2X 81+ Gold Players Pack</t>
+          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 30 separate matches in the season 1: ones to watch exhibition.||score in 30</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4196,21 +4196,21 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Score in 20</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Score in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2X 81+ Gold Players Pack / 2X 80+ Gold Players Pack / 80+ Gold Player Pack</t>
+          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||score in 20 separate matches in the season 1: ones to watch exhibition.||score in 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4272,21 +4272,21 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Assist 20</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Assist in 20 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2X 80+ Gold Players Pack / 80+ Gold Player Pack / 2X 78+ Gold Players Pack</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 20 separate matches in the season 1: ones to watch exhibition.||assist 20</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4348,21 +4348,21 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Assist 15</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Assist in 15 separate matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / 2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack</t>
+          <t>Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||assist in 15 separate matches in the season 1: ones to watch exhibition.||assist 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4424,21 +4424,21 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>The Final Challenge</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Play 15 matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2X 78+ Gold Players Pack / 2X 75+ Gold Players Pack / Consumables Pack</t>
+          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 15 matches in the season 1: ones to watch exhibition.||play 15</t>
+          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4500,21 +4500,21 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Finesse</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / Consumable</t>
+          <t>Evo Unlock / Consumable / 1,500 Coins</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 5 matches in the season 1: ones to watch exhibition.||play 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4576,21 +4576,21 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Serial Winner</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in the Season 1: Ones to Watch Exhibition.</t>
+          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / Consumable</t>
+          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Season 1: Ones to Watch Exhibition - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/88-season-1-ones-to-watch-exhibition/||play 1 match in the season 1: ones to watch exhibition.||play 1</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4652,21 +4652,21 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>The Final Challenge</t>
+          <t>PL Scorer</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Win 4 matches in the Ones We Watched Legendary Challenge.</t>
+          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1x 3x 80+ Gold Players Pack / 1x 2x 78+ Gold Players Pack / 1x 15x 75+ LALIGA Gold Players Pack / 10X 75+ Gold Players Pack</t>
+          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Legendary Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/83-ones-we-watched-legendary-challenge/||win 4 matches in the ones we watched legendary challenge.||the final challenge</t>
+          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Finesse</t>
+          <t>Top Scorer</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Score two Finesse goals in 3 separate matches in the Ones We Watched World Class Challenge.</t>
+          <t>Score in 5 separate matches while having min. 1 Serie A player in your starting XI in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / Consumable / 1,500 Coins</t>
+          <t>1x 2x 75+ Gold Players Pack / 1x Consumables Pack / 1x 3x 78+ Serie A Gold Players Pack / 2X 75+ Gold Players Pack</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score two finesse goals in 3 separate matches in the ones we watched world class challenge.||finesse</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||score in 5 separate matches while having min. 1 serie a player in your starting xi in the ones we watched professional challenge.||top scorer</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Serial Winner</t>
+          <t>Assister</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Assist 1 goal while having min. 1 Spanish player in your starting XI in the Ones We Watched World Class Challenge.</t>
+          <t>Assist 2 goals in 1 match in the Ones We Watched Professional Challenge.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Consumable / 1,500 Coins / 2X 75+ Gold Players Pack</t>
+          <t>1,750 Coins / Consumables Pack / Consumable</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Professional Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||assist 1 goal while having min. 1 spanish player in your starting xi in the ones we watched world class challenge.||serial winner</t>
+          <t>https://www.fut.gg/objectives/seasonal/86-ones-we-watched-professional-challenge/||assist 2 goals in 1 match in the ones we watched professional challenge.||assister</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -4880,21 +4880,21 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>PL Scorer</t>
+          <t>Assist 3</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Score with a Premier League player in the Ones We Watched World Class Challenge.</t>
+          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>1,500 Coins / 2X 75+ Gold Players Pack</t>
+          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G013</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched World Class Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/82-ones-we-watched-world-class-challenge/||score with a premier league player in the ones we watched world class challenge.||pl scorer</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4956,21 +4956,21 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Assist 3</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Assist 3 goals in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>2X 75+ Gold Players Pack / Consumables Pack / 750 Coins</t>
+          <t>Consumables Pack / 750 Coins / Consumable</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||assist 3 goals in the ones we watched semi-pro challenge.||assist 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5032,21 +5032,21 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Assist in 3</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches with min. 1 Spanish player in your starting XI in the Ones We Watched Semi-Pro Challenge.</t>
+          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 750 Coins / Consumable</t>
+          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>G013</t>
+          <t>G014</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Semi-Pro Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/85-ones-we-watched-semi-pro-challenge/||play 2 matches with min. 1 spanish player in your starting xi in the ones we watched semi-pro challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5108,21 +5108,21 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Assist in 3 separate matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>80+ Gold Player Pack / Consumables Pack / 500 Coins</t>
+          <t>Consumables Pack / 500 Coins / Consumable</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||assist in 3 separate matches in the ones we watched kick off challenge.||assist in 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5184,21 +5184,21 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches in the Ones We Watched Kick Off Challenge.</t>
+          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Consumables Pack / 500 Coins / Consumable</t>
+          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -5209,17 +5209,17 @@
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>G014</t>
+          <t>G015</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Ones We Watched Kick Off Challenge - EA SPORTS FC 27 Objectives</t>
+          <t>Ones We Watched Challenge Completionist - EA SPORTS FC 27 Objectives</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/84-ones-we-watched-kick-off-challenge/||play 2 matches in the ones we watched kick off challenge.||play 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5260,21 +5260,21 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Complete the Ones We Watched World Class Challenge objective</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched Legendary Challenge objective.</t>
+          <t>Complete the Ones We Watched World Class Challenge objective.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>16,000 Coins / 5,000 Coins / 4,500 Coins</t>
+          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 25 days</t>
+          <t>Expires in 24 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched legendary challenge objective.||complete the ones we watched legendary challenge objective.</t>
+          <t>https://www.fut.gg/objectives/seasonal/87-ones-we-watched-challenge-completionist/||complete the ones we watched world class challenge objective.||complete the ones we watched world class challenge objective</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5336,21 +5336,21 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective</t>
+          <t>Complete the Ones We Watched Professional Challenge objectiv</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Complete the Ones We Watched World Class Challenge objective.</t>
+          <t>Complete the Ones We Watched Professional Challenge objective.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5,000 Coins / 4,500 Coins / 4,000 Coins</t>
+          <t>4,500 Coins / 4,000 Coins / 2,500 Coins</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r=